--- a/PATXOT 512/Septiembre/PATXOT 521 Septiembre.xlsx
+++ b/PATXOT 512/Septiembre/PATXOT 521 Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E022D1-3448-4832-81C8-A58423EF4291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F43BF9B-6BDA-412C-863E-4C84D8004346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="PRORRATEO EXPRESS" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">edesur!$A$1:$H$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PRORRATEO EXPRESS'!$A$1:$L$16</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="137">
   <si>
     <t>UF</t>
   </si>
@@ -422,49 +422,25 @@
     <t>Obra</t>
   </si>
   <si>
-    <t>LIQUIDACIÓN EXPENSAS AGOSTO 2025</t>
-  </si>
-  <si>
     <t>MANO DE OBRA (2/2)</t>
   </si>
   <si>
-    <t>AYSA - Agosto</t>
-  </si>
-  <si>
-    <t>AYSA - Julio</t>
-  </si>
-  <si>
-    <t>Edesur - Julio</t>
-  </si>
-  <si>
-    <t>Edesur - Agosto</t>
-  </si>
-  <si>
-    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Agosto</t>
-  </si>
-  <si>
-    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Julio</t>
-  </si>
-  <si>
-    <t>Honorarios Administracion - Julio</t>
-  </si>
-  <si>
-    <t>Honorarios Administracion - Agosto</t>
-  </si>
-  <si>
-    <t>Honorarios Administracion - Junio</t>
-  </si>
-  <si>
-    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Junio</t>
-  </si>
-  <si>
-    <t>AYSA - Junio</t>
-  </si>
-  <si>
-    <t>Edesur - Junio</t>
-  </si>
-  <si>
     <t>EDESUR:</t>
+  </si>
+  <si>
+    <t>LIQUIDACIÓN EXPENSAS septiembre 2025</t>
+  </si>
+  <si>
+    <t>AYSA - septiembre</t>
+  </si>
+  <si>
+    <t>Honorarios Administracion - septiembre</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - septiembre</t>
+  </si>
+  <si>
+    <t>Edesur - septiembre</t>
   </si>
 </sst>
 </file>
@@ -1749,6 +1725,47 @@
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1759,12 +1776,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1785,35 +1796,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1829,12 +1811,6 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1844,11 +1820,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2219,7 +2195,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F60"/>
+  <dimension ref="A2:F52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2254,7 +2230,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="169" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
@@ -2298,356 +2274,270 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="75" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="211">
-        <v>79724.34</v>
+      <c r="C17" s="174">
+        <v>91854.86</v>
       </c>
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="75" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="87" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="84">
-        <v>84579.51</v>
-      </c>
-      <c r="D18" s="48"/>
-      <c r="F18" s="14"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="60">
+        <f>SUM(C17:C17)</f>
+        <v>91854.86</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="75" t="s">
-        <v>142</v>
-      </c>
-      <c r="B19" s="87" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="84">
-        <v>74186.03</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="14"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="88"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="60">
-        <f>SUM(C17:C19)</f>
-        <v>238489.87999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="86" t="s">
+      <c r="A19" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="87"/>
-      <c r="C21" s="90"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="90"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" s="91"/>
+      <c r="C20" s="84">
+        <v>37000</v>
+      </c>
+      <c r="F20" s="22"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="B21" s="91"/>
+      <c r="C21" s="84">
+        <v>36534.6</v>
+      </c>
+      <c r="F21" s="22"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="75" t="s">
-        <v>139</v>
-      </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="84">
-        <v>30000</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="B22" s="87"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="14"/>
       <c r="F22" s="22"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="75" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="91"/>
-      <c r="C23" s="84">
-        <v>30000</v>
+      <c r="A23" s="88"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="60">
+        <f>SUM(C19:C22)</f>
+        <v>73534.600000000006</v>
       </c>
       <c r="F23" s="22"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="75" t="s">
-        <v>140</v>
-      </c>
-      <c r="B24" s="91"/>
-      <c r="C24" s="84">
-        <v>30000</v>
+      <c r="A24" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="79"/>
+      <c r="C24" s="92">
+        <f>+C23+C18</f>
+        <v>165389.46000000002</v>
       </c>
       <c r="F24" s="22"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="75" t="s">
+      <c r="C25" s="61"/>
+      <c r="F25" s="22"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="61"/>
+      <c r="F26" s="22"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="75"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="84"/>
+      <c r="F27" s="22"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="75"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="85"/>
+      <c r="F28" s="22"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="75"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="85"/>
+      <c r="F29" s="22"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C30" s="63"/>
+      <c r="F30" s="22"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="23"/>
+      <c r="C31" s="24">
+        <f>+C27+C28+C29+C30</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="14"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="34"/>
+      <c r="C33" s="35">
+        <f>+C31+C24</f>
+        <v>165389.46000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="146" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="147"/>
+      <c r="C35" s="148"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="144" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="145">
+        <v>-406759.6</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="32">
+        <f>'prorrateo '!F15</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>136</v>
       </c>
-      <c r="B25" s="91"/>
-      <c r="C25" s="84">
-        <v>36534.6</v>
-      </c>
-      <c r="F25" s="22"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="B26" s="91"/>
-      <c r="C26" s="84">
-        <v>36534.6</v>
-      </c>
-      <c r="F26" s="22"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="75" t="s">
-        <v>141</v>
-      </c>
-      <c r="B27" s="91"/>
-      <c r="C27" s="84">
-        <v>36534.6</v>
-      </c>
-      <c r="F27" s="22"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="75" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="87"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="22"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="88"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="60">
-        <f>SUM(C21:C28)</f>
-        <v>199603.80000000002</v>
-      </c>
-      <c r="F29" s="22"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="79" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="79"/>
-      <c r="C30" s="92">
-        <f>+C29+C20</f>
-        <v>438093.68</v>
-      </c>
-      <c r="F30" s="22"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C31" s="61"/>
-      <c r="F31" s="22"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="61"/>
-      <c r="F32" s="22"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="75"/>
-      <c r="B33" s="75"/>
-      <c r="C33" s="84"/>
-      <c r="F33" s="22"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="75"/>
-      <c r="B34" s="75"/>
-      <c r="C34" s="85"/>
-      <c r="F34" s="22"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
-      <c r="B35" s="75"/>
-      <c r="C35" s="85"/>
-      <c r="F35" s="22"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C36" s="63"/>
-      <c r="F36" s="22"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="24">
-        <f>+C33+C34+C35+C36</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="14"/>
+      <c r="C38" s="93">
+        <v>-229765.65</v>
+      </c>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="35">
-        <f>+C37+C30</f>
-        <v>438093.68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="146" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="147"/>
-      <c r="C41" s="148"/>
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="93">
+        <f>-(C24-C22)</f>
+        <v>-165389.46000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="33"/>
+      <c r="C40" s="40">
+        <f>SUM(C36:C39)</f>
+        <v>-801914.71</v>
+      </c>
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="19"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="20"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="144" t="s">
-        <v>10</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="145">
-        <v>8056.9037403397379</v>
-      </c>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
+      <c r="A42" s="19"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="20"/>
+      <c r="F42" s="94"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="32">
-        <f>'prorrateo '!F15</f>
-        <v>114809.90303832441</v>
-      </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" s="93">
-        <v>-133418.04</v>
-      </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
+      <c r="A43" s="19"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="20"/>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="74"/>
+      <c r="C44" s="77">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>134</v>
-      </c>
-      <c r="C45" s="93">
-        <v>-125968.51</v>
-      </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
+      <c r="A45" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="75"/>
+      <c r="C45" s="82">
+        <f>-C31</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>143</v>
-      </c>
-      <c r="C46" s="93">
-        <v>-10296.959999999999</v>
-      </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
+      <c r="A46" s="75"/>
+      <c r="B46" s="75"/>
+      <c r="C46" s="82"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-      <c r="C47" s="93">
-        <f>-(C30-C28)</f>
-        <v>-438093.68</v>
-      </c>
+      <c r="A47" s="75"/>
+      <c r="B47" s="75"/>
+      <c r="C47" s="83"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" s="33"/>
-      <c r="C48" s="40">
-        <f>SUM(C42:C47)</f>
-        <v>-584910.38322133583</v>
-      </c>
-      <c r="D48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="19"/>
+      <c r="A48" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="76"/>
+      <c r="C48" s="78">
+        <f>SUM(C44:C47)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="18"/>
       <c r="B49" s="18"/>
-      <c r="C49" s="20"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="19"/>
+      <c r="C49" s="18"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="18"/>
       <c r="B50" s="18"/>
-      <c r="C50" s="20"/>
-      <c r="F50" s="94"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="19"/>
+      <c r="C50" s="18"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="18"/>
       <c r="B51" s="18"/>
-      <c r="C51" s="20"/>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="73" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="74"/>
-      <c r="C52" s="77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="75" t="s">
-        <v>63</v>
-      </c>
-      <c r="B53" s="75"/>
-      <c r="C53" s="82">
-        <f>-C37</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="75"/>
-      <c r="B54" s="75"/>
-      <c r="C54" s="82"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="75"/>
-      <c r="B55" s="75"/>
-      <c r="C55" s="83"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="B56" s="76"/>
-      <c r="C56" s="78">
-        <f>SUM(C52:C55)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="18"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="18"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="18"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
+      <c r="C51" s="18"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2688,16 +2578,13 @@
         <v>48</v>
       </c>
       <c r="E1" s="14">
-        <v>438093.68</v>
-      </c>
-      <c r="H1" s="212" t="s">
-        <v>144</v>
-      </c>
-      <c r="I1" s="212"/>
-      <c r="J1" s="14">
-        <f>-('detalle y gastos'!C44+'detalle y gastos'!C45+'detalle y gastos'!C46)</f>
-        <v>269683.51</v>
-      </c>
+        <v>165389.46000000002</v>
+      </c>
+      <c r="H1" s="175" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1" s="175"/>
+      <c r="J1" s="14"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="97">
@@ -2717,14 +2604,14 @@
       <c r="L2" s="102"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="199" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="183"/>
-      <c r="C3" s="178" t="s">
+      <c r="B3" s="200"/>
+      <c r="C3" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="180" t="s">
+      <c r="D3" s="197" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2733,19 +2620,19 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="178" t="s">
+      <c r="G3" s="189" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="176" t="s">
+      <c r="I3" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="186" t="s">
+      <c r="J3" s="191" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="178" t="s">
+      <c r="K3" s="189" t="s">
         <v>42</v>
       </c>
       <c r="L3" s="45" t="s">
@@ -2753,32 +2640,32 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="184"/>
-      <c r="B4" s="185"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="181"/>
+      <c r="A4" s="201"/>
+      <c r="B4" s="202"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="198"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="179"/>
+      <c r="G4" s="190"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="177"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="179"/>
+      <c r="I4" s="196"/>
+      <c r="J4" s="192"/>
+      <c r="K4" s="190"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="174">
+      <c r="A5" s="193">
         <v>1</v>
       </c>
-      <c r="B5" s="175"/>
+      <c r="B5" s="194"/>
       <c r="C5" s="110" t="s">
         <v>65</v>
       </c>
@@ -2786,39 +2673,36 @@
       <c r="E5" s="149">
         <v>41531.40466575251</v>
       </c>
-      <c r="F5" s="150">
-        <f t="shared" ref="F5:F9" si="0">E5</f>
-        <v>41531.40466575251</v>
-      </c>
+      <c r="F5" s="150"/>
       <c r="G5" s="151">
         <f>E5-F5</f>
-        <v>0</v>
+        <v>41531.40466575251</v>
       </c>
       <c r="H5" s="151">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>0</v>
+        <v>1661.2561866301005</v>
       </c>
       <c r="I5" s="95">
         <v>13.8</v>
       </c>
       <c r="J5" s="96">
         <f>E$1*I5/100</f>
-        <v>60456.927839999997</v>
+        <v>22823.745480000005</v>
       </c>
       <c r="K5" s="142">
         <f>J$1*I5/100</f>
-        <v>37216.324380000005</v>
+        <v>0</v>
       </c>
       <c r="L5" s="103">
         <f>G5+H5+J5+K5</f>
-        <v>97673.252219999995</v>
+        <v>66016.406332382612</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="174">
+      <c r="A6" s="193">
         <v>2</v>
       </c>
-      <c r="B6" s="175"/>
+      <c r="B6" s="194"/>
       <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
@@ -2828,39 +2712,36 @@
       <c r="E6" s="149">
         <v>36166.928390240799</v>
       </c>
-      <c r="F6" s="150">
-        <f t="shared" si="0"/>
+      <c r="F6" s="150"/>
+      <c r="G6" s="151">
+        <f t="shared" ref="G6:G14" si="0">E6-F6</f>
         <v>36166.928390240799</v>
       </c>
-      <c r="G6" s="151">
-        <f t="shared" ref="G6:G14" si="1">E6-F6</f>
-        <v>0</v>
-      </c>
       <c r="H6" s="151">
-        <f t="shared" ref="H6:H14" si="2">IF(G6&gt;0,G6*4%,0)</f>
-        <v>0</v>
+        <f t="shared" ref="H6:H14" si="1">IF(G6&gt;0,G6*4%,0)</f>
+        <v>1446.6771356096319</v>
       </c>
       <c r="I6" s="95">
         <v>11.86</v>
       </c>
       <c r="J6" s="96">
-        <f t="shared" ref="J6:J14" si="3">E$1*I6/100</f>
-        <v>51957.910447999995</v>
+        <f t="shared" ref="J6:J14" si="2">E$1*I6/100</f>
+        <v>19615.189956000002</v>
       </c>
       <c r="K6" s="142">
-        <f t="shared" ref="K6:K14" si="4">J$1*I6/100</f>
-        <v>31984.464285999999</v>
+        <f t="shared" ref="K6:K14" si="3">J$1*I6/100</f>
+        <v>0</v>
       </c>
       <c r="L6" s="103">
-        <f t="shared" ref="L6:L14" si="5">G6+H6+J6+K6</f>
-        <v>83942.374733999997</v>
+        <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
+        <v>57228.795481850429</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="174">
+      <c r="A7" s="193">
         <v>3</v>
       </c>
-      <c r="B7" s="175"/>
+      <c r="B7" s="194"/>
       <c r="C7" s="110" t="s">
         <v>66</v>
       </c>
@@ -2872,34 +2753,34 @@
       </c>
       <c r="F7" s="150"/>
       <c r="G7" s="151">
+        <f t="shared" si="0"/>
+        <v>37894.033173585289</v>
+      </c>
+      <c r="H7" s="151">
         <f t="shared" si="1"/>
-        <v>37894.033173585289</v>
-      </c>
-      <c r="H7" s="151">
-        <f t="shared" si="2"/>
         <v>1515.7613269434116</v>
       </c>
       <c r="I7" s="95">
         <v>12.46</v>
       </c>
       <c r="J7" s="96">
+        <f t="shared" si="2"/>
+        <v>20607.526716000004</v>
+      </c>
+      <c r="K7" s="142">
         <f t="shared" si="3"/>
-        <v>54586.472527999998</v>
-      </c>
-      <c r="K7" s="142">
+        <v>0</v>
+      </c>
+      <c r="L7" s="103">
         <f t="shared" si="4"/>
-        <v>33602.565346000003</v>
-      </c>
-      <c r="L7" s="103">
-        <f t="shared" si="5"/>
-        <v>127598.83237452871</v>
+        <v>60017.321216528711</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="174">
+      <c r="A8" s="193">
         <v>4</v>
       </c>
-      <c r="B8" s="175"/>
+      <c r="B8" s="194"/>
       <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
@@ -2911,34 +2792,34 @@
       </c>
       <c r="F8" s="150"/>
       <c r="G8" s="151">
+        <f t="shared" si="0"/>
+        <v>44723.725567140471</v>
+      </c>
+      <c r="H8" s="151">
         <f t="shared" si="1"/>
-        <v>44723.725567140471</v>
-      </c>
-      <c r="H8" s="151">
-        <f t="shared" si="2"/>
         <v>1788.949022685619</v>
       </c>
       <c r="I8" s="95">
         <v>14.75</v>
       </c>
       <c r="J8" s="96">
+        <f t="shared" si="2"/>
+        <v>24394.945350000002</v>
+      </c>
+      <c r="K8" s="142">
         <f t="shared" si="3"/>
-        <v>64618.817800000004</v>
-      </c>
-      <c r="K8" s="142">
+        <v>0</v>
+      </c>
+      <c r="L8" s="103">
         <f t="shared" si="4"/>
-        <v>39778.317725000001</v>
-      </c>
-      <c r="L8" s="103">
-        <f t="shared" si="5"/>
-        <v>150909.8101148261</v>
+        <v>70907.619939826094</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="174">
+      <c r="A9" s="193">
         <v>5</v>
       </c>
-      <c r="B9" s="175"/>
+      <c r="B9" s="194"/>
       <c r="C9" s="110" t="s">
         <v>68</v>
       </c>
@@ -2948,39 +2829,36 @@
       <c r="E9" s="149">
         <v>37111.569982331108</v>
       </c>
-      <c r="F9" s="150">
+      <c r="F9" s="150"/>
+      <c r="G9" s="151">
         <f t="shared" si="0"/>
         <v>37111.569982331108</v>
       </c>
-      <c r="G9" s="151">
+      <c r="H9" s="151">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="151">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1484.4627992932444</v>
       </c>
       <c r="I9" s="95">
         <v>12.41</v>
       </c>
       <c r="J9" s="96">
+        <f t="shared" si="2"/>
+        <v>20524.831986000001</v>
+      </c>
+      <c r="K9" s="142">
         <f t="shared" si="3"/>
-        <v>54367.425687999996</v>
-      </c>
-      <c r="K9" s="142">
-        <f t="shared" si="4"/>
-        <v>33467.723591000002</v>
+        <v>0</v>
       </c>
       <c r="L9" s="103">
         <f>G9+H9+J9+K9</f>
-        <v>87835.149279000005</v>
+        <v>59120.864767624356</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="174">
+      <c r="A10" s="193">
         <v>6</v>
       </c>
-      <c r="B10" s="175"/>
+      <c r="B10" s="194"/>
       <c r="C10" s="110" t="s">
         <v>69</v>
       </c>
@@ -2990,34 +2868,34 @@
       </c>
       <c r="F10" s="150"/>
       <c r="G10" s="151">
+        <f t="shared" si="0"/>
+        <v>37332.293419986621</v>
+      </c>
+      <c r="H10" s="151">
         <f t="shared" si="1"/>
-        <v>37332.293419986621</v>
-      </c>
-      <c r="H10" s="151">
-        <f t="shared" si="2"/>
         <v>1493.2917367994648</v>
       </c>
       <c r="I10" s="95">
         <v>12.48</v>
       </c>
       <c r="J10" s="96">
+        <f t="shared" si="2"/>
+        <v>20640.604608000001</v>
+      </c>
+      <c r="K10" s="142">
         <f t="shared" si="3"/>
-        <v>54674.091264000002</v>
-      </c>
-      <c r="K10" s="142">
+        <v>0</v>
+      </c>
+      <c r="L10" s="103">
         <f t="shared" si="4"/>
-        <v>33656.502048000002</v>
-      </c>
-      <c r="L10" s="103">
-        <f t="shared" si="5"/>
-        <v>127156.17846878609</v>
+        <v>59466.18976478609</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="174">
+      <c r="A11" s="193">
         <v>7</v>
       </c>
-      <c r="B11" s="175"/>
+      <c r="B11" s="194"/>
       <c r="C11" s="110" t="s">
         <v>70</v>
       </c>
@@ -3027,34 +2905,34 @@
       </c>
       <c r="F11" s="150"/>
       <c r="G11" s="151">
+        <f t="shared" si="0"/>
+        <v>54686.953726963213</v>
+      </c>
+      <c r="H11" s="151">
         <f t="shared" si="1"/>
-        <v>54686.953726963213</v>
-      </c>
-      <c r="H11" s="151">
-        <f t="shared" si="2"/>
         <v>2187.4781490785285</v>
       </c>
       <c r="I11" s="95">
         <v>18.260000000000002</v>
       </c>
       <c r="J11" s="96">
+        <f t="shared" si="2"/>
+        <v>30200.115396000008</v>
+      </c>
+      <c r="K11" s="142">
         <f t="shared" si="3"/>
-        <v>79995.905968000006</v>
-      </c>
-      <c r="K11" s="142">
+        <v>0</v>
+      </c>
+      <c r="L11" s="103">
         <f t="shared" si="4"/>
-        <v>49244.208926000007</v>
-      </c>
-      <c r="L11" s="103">
-        <f t="shared" si="5"/>
-        <v>186114.54677004175</v>
+        <v>87074.54727204176</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="174" t="s">
+      <c r="A12" s="193" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="175"/>
+      <c r="B12" s="194"/>
       <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -3065,34 +2943,34 @@
       </c>
       <c r="F12" s="150"/>
       <c r="G12" s="151">
+        <f t="shared" si="0"/>
+        <v>3895.6564420000004</v>
+      </c>
+      <c r="H12" s="151">
         <f t="shared" si="1"/>
-        <v>3895.6564420000004</v>
-      </c>
-      <c r="H12" s="151">
-        <f t="shared" si="2"/>
         <v>155.82625768000003</v>
       </c>
       <c r="I12" s="95">
         <v>1.34</v>
       </c>
       <c r="J12" s="96">
+        <f t="shared" si="2"/>
+        <v>2216.2187640000002</v>
+      </c>
+      <c r="K12" s="142">
         <f t="shared" si="3"/>
-        <v>5870.455312</v>
-      </c>
-      <c r="K12" s="142">
+        <v>0</v>
+      </c>
+      <c r="L12" s="103">
         <f t="shared" si="4"/>
-        <v>3613.7590340000002</v>
-      </c>
-      <c r="L12" s="103">
-        <f t="shared" si="5"/>
-        <v>13535.697045680001</v>
+        <v>6267.7014636800004</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="174" t="s">
+      <c r="A13" s="193" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="175"/>
+      <c r="B13" s="194"/>
       <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3103,34 +2981,34 @@
       </c>
       <c r="F13" s="150"/>
       <c r="G13" s="151">
+        <f t="shared" si="0"/>
+        <v>3837.5123159999998</v>
+      </c>
+      <c r="H13" s="151">
         <f t="shared" si="1"/>
-        <v>3837.5123159999998</v>
-      </c>
-      <c r="H13" s="151">
-        <f t="shared" si="2"/>
         <v>153.50049264</v>
       </c>
       <c r="I13" s="95">
         <v>1.32</v>
       </c>
       <c r="J13" s="96">
+        <f t="shared" si="2"/>
+        <v>2183.1408720000004</v>
+      </c>
+      <c r="K13" s="142">
         <f t="shared" si="3"/>
-        <v>5782.8365760000006</v>
-      </c>
-      <c r="K13" s="142">
+        <v>0</v>
+      </c>
+      <c r="L13" s="103">
         <f t="shared" si="4"/>
-        <v>3559.8223320000002</v>
-      </c>
-      <c r="L13" s="103">
-        <f t="shared" si="5"/>
-        <v>13333.671716640001</v>
+        <v>6174.1536806399999</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="174" t="s">
+      <c r="A14" s="193" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="175"/>
+      <c r="B14" s="194"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3141,27 +3019,27 @@
       </c>
       <c r="F14" s="150"/>
       <c r="G14" s="151">
+        <f t="shared" si="0"/>
+        <v>3837.5123159999998</v>
+      </c>
+      <c r="H14" s="151">
         <f t="shared" si="1"/>
-        <v>3837.5123159999998</v>
-      </c>
-      <c r="H14" s="151">
-        <f t="shared" si="2"/>
         <v>153.50049264</v>
       </c>
       <c r="I14" s="95">
         <v>1.32</v>
       </c>
       <c r="J14" s="96">
+        <f t="shared" si="2"/>
+        <v>2183.1408720000004</v>
+      </c>
+      <c r="K14" s="142">
         <f t="shared" si="3"/>
-        <v>5782.8365760000006</v>
-      </c>
-      <c r="K14" s="142">
+        <v>0</v>
+      </c>
+      <c r="L14" s="103">
         <f t="shared" si="4"/>
-        <v>3559.8223320000002</v>
-      </c>
-      <c r="L14" s="103">
-        <f t="shared" si="5"/>
-        <v>13333.671716640001</v>
+        <v>6174.1536806399999</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3177,28 +3055,28 @@
       </c>
       <c r="F15" s="107">
         <f>SUM(F5:F14)</f>
-        <v>114809.90303832441</v>
+        <v>0</v>
       </c>
       <c r="G15" s="107"/>
       <c r="H15" s="108">
         <f>SUM(H5:H14)</f>
-        <v>7448.3074784670234</v>
+        <v>12040.703600000001</v>
       </c>
       <c r="I15" s="109">
-        <f t="shared" ref="I15" si="6">SUM(I5:I14)</f>
+        <f t="shared" ref="I15" si="5">SUM(I5:I14)</f>
         <v>100</v>
       </c>
       <c r="J15" s="39">
         <f>SUM(J5:J14)</f>
-        <v>438093.67999999993</v>
+        <v>165389.46</v>
       </c>
       <c r="K15" s="42">
         <f>SUM(K5:K11)</f>
-        <v>258950.106302</v>
+        <v>0</v>
       </c>
       <c r="L15" s="42">
         <f>SUM(L5:L14)</f>
-        <v>901433.18444014259</v>
+        <v>478447.75360000005</v>
       </c>
     </row>
     <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
@@ -3344,7 +3222,7 @@
         <v>0.122</v>
       </c>
       <c r="J23" s="44">
-        <f t="shared" ref="J23:J29" si="7">0*I23</f>
+        <f t="shared" ref="J23:J29" si="6">0*I23</f>
         <v>0</v>
       </c>
       <c r="K23" s="41"/>
@@ -3379,7 +3257,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="J24" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K24" s="41"/>
@@ -3410,7 +3288,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="J25" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K25" s="41"/>
@@ -3441,7 +3319,7 @@
         <v>0.13700000000000001</v>
       </c>
       <c r="J26" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K26" s="41"/>
@@ -3472,7 +3350,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="J27" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K27" s="41"/>
@@ -3506,7 +3384,7 @@
         <v>0.127</v>
       </c>
       <c r="J28" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K28" s="41"/>
@@ -3540,7 +3418,7 @@
         <v>0.127</v>
       </c>
       <c r="J29" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K29" s="41"/>
@@ -3569,11 +3447,11 @@
         <v>0</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" ref="I30:J30" si="8">SUM(I22:I29)</f>
+        <f t="shared" ref="I30:J30" si="7">SUM(I22:I29)</f>
         <v>1</v>
       </c>
       <c r="J30" s="39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K30" s="42"/>
@@ -3590,15 +3468,15 @@
     <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="188" t="s">
+      <c r="E32" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="189"/>
-      <c r="G32" s="189"/>
-      <c r="H32" s="189"/>
-      <c r="I32" s="189"/>
-      <c r="J32" s="189"/>
-      <c r="K32" s="190"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="179"/>
       <c r="L32" s="152"/>
       <c r="M32" s="153"/>
       <c r="N32"/>
@@ -3606,15 +3484,15 @@
     <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="191" t="s">
+      <c r="E33" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="189"/>
-      <c r="G33" s="189"/>
-      <c r="H33" s="189"/>
-      <c r="I33" s="189"/>
-      <c r="J33" s="189"/>
-      <c r="K33" s="190"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="179"/>
       <c r="L33" s="154"/>
       <c r="M33" s="155"/>
       <c r="N33"/>
@@ -3669,15 +3547,15 @@
     <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="192" t="s">
+      <c r="E37" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="193"/>
-      <c r="G37" s="193"/>
-      <c r="H37" s="193"/>
-      <c r="I37" s="193"/>
-      <c r="J37" s="193"/>
-      <c r="K37" s="194"/>
+      <c r="F37" s="184"/>
+      <c r="G37" s="184"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="184"/>
+      <c r="J37" s="184"/>
+      <c r="K37" s="185"/>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37"/>
@@ -3715,10 +3593,10 @@
         <v>45674</v>
       </c>
       <c r="K39" s="155"/>
-      <c r="L39" s="195" t="s">
+      <c r="L39" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="196"/>
+      <c r="M39" s="187"/>
       <c r="N39"/>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.25">
@@ -3749,8 +3627,8 @@
       <c r="I41" s="157"/>
       <c r="J41" s="157"/>
       <c r="K41" s="155"/>
-      <c r="L41" s="197"/>
-      <c r="M41" s="196"/>
+      <c r="L41" s="188"/>
+      <c r="M41" s="187"/>
       <c r="N41"/>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.25">
@@ -3765,7 +3643,7 @@
       <c r="I42" s="157"/>
       <c r="J42" s="163">
         <f>J7</f>
-        <v>54586.472527999998</v>
+        <v>20607.526716000004</v>
       </c>
       <c r="K42" s="155"/>
       <c r="L42" s="154"/>
@@ -3784,7 +3662,7 @@
       <c r="I43" s="157"/>
       <c r="J43" s="163">
         <f>K7</f>
-        <v>33602.565346000003</v>
+        <v>0</v>
       </c>
       <c r="K43" s="155"/>
       <c r="L43" s="154"/>
@@ -3915,18 +3793,18 @@
     <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="198" t="s">
+      <c r="E52" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="199"/>
-      <c r="G52" s="199"/>
-      <c r="H52" s="199"/>
-      <c r="I52" s="199"/>
-      <c r="J52" s="200">
+      <c r="F52" s="177"/>
+      <c r="G52" s="177"/>
+      <c r="H52" s="177"/>
+      <c r="I52" s="177"/>
+      <c r="J52" s="178">
         <f>SUM(J42:J51)</f>
-        <v>127674.63237452871</v>
-      </c>
-      <c r="K52" s="190"/>
+        <v>60093.121216528714</v>
+      </c>
+      <c r="K52" s="179"/>
       <c r="L52" s="167"/>
       <c r="M52" s="168"/>
       <c r="N52"/>
@@ -3938,28 +3816,28 @@
     </row>
     <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="188" t="s">
+      <c r="E56" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="189"/>
-      <c r="G56" s="189"/>
-      <c r="H56" s="189"/>
-      <c r="I56" s="189"/>
-      <c r="J56" s="189"/>
-      <c r="K56" s="190"/>
+      <c r="F56" s="181"/>
+      <c r="G56" s="181"/>
+      <c r="H56" s="181"/>
+      <c r="I56" s="181"/>
+      <c r="J56" s="181"/>
+      <c r="K56" s="179"/>
       <c r="L56" s="152"/>
       <c r="M56" s="153"/>
     </row>
     <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="191" t="s">
+      <c r="E57" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="189"/>
-      <c r="G57" s="189"/>
-      <c r="H57" s="189"/>
-      <c r="I57" s="189"/>
-      <c r="J57" s="189"/>
-      <c r="K57" s="190"/>
+      <c r="F57" s="181"/>
+      <c r="G57" s="181"/>
+      <c r="H57" s="181"/>
+      <c r="I57" s="181"/>
+      <c r="J57" s="181"/>
+      <c r="K57" s="179"/>
       <c r="L57" s="154"/>
       <c r="M57" s="155"/>
     </row>
@@ -4002,15 +3880,15 @@
       <c r="M60" s="155"/>
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="192" t="s">
+      <c r="E61" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="193"/>
-      <c r="G61" s="193"/>
-      <c r="H61" s="193"/>
-      <c r="I61" s="193"/>
-      <c r="J61" s="193"/>
-      <c r="K61" s="194"/>
+      <c r="F61" s="184"/>
+      <c r="G61" s="184"/>
+      <c r="H61" s="184"/>
+      <c r="I61" s="184"/>
+      <c r="J61" s="184"/>
+      <c r="K61" s="185"/>
       <c r="L61" s="154"/>
       <c r="M61" s="155"/>
     </row>
@@ -4042,10 +3920,10 @@
         <v>45674</v>
       </c>
       <c r="K63" s="155"/>
-      <c r="L63" s="195" t="s">
+      <c r="L63" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="196"/>
+      <c r="M63" s="187"/>
     </row>
     <row r="64" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E64" s="154" t="s">
@@ -4070,8 +3948,8 @@
       <c r="I65" s="157"/>
       <c r="J65" s="157"/>
       <c r="K65" s="155"/>
-      <c r="L65" s="197"/>
-      <c r="M65" s="196"/>
+      <c r="L65" s="188"/>
+      <c r="M65" s="187"/>
     </row>
     <row r="66" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E66" s="154" t="s">
@@ -4083,7 +3961,7 @@
       <c r="I66" s="157"/>
       <c r="J66" s="163">
         <f>J8</f>
-        <v>64618.817800000004</v>
+        <v>24394.945350000002</v>
       </c>
       <c r="K66" s="155"/>
       <c r="L66" s="154"/>
@@ -4099,7 +3977,7 @@
       <c r="I67" s="157"/>
       <c r="J67" s="163">
         <f>K8</f>
-        <v>39778.317725000001</v>
+        <v>0</v>
       </c>
       <c r="K67" s="155"/>
       <c r="L67" s="154"/>
@@ -4198,45 +4076,45 @@
       <c r="M75" s="166"/>
     </row>
     <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="198" t="s">
+      <c r="E76" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="199"/>
-      <c r="G76" s="199"/>
-      <c r="H76" s="199"/>
-      <c r="I76" s="199"/>
-      <c r="J76" s="200">
+      <c r="F76" s="177"/>
+      <c r="G76" s="177"/>
+      <c r="H76" s="177"/>
+      <c r="I76" s="177"/>
+      <c r="J76" s="178">
         <f>SUM(J66:J75)</f>
-        <v>104397.13552500001</v>
-      </c>
-      <c r="K76" s="190"/>
+        <v>24394.945350000002</v>
+      </c>
+      <c r="K76" s="179"/>
       <c r="L76" s="167"/>
       <c r="M76" s="168"/>
     </row>
     <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="188" t="s">
+      <c r="E83" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="189"/>
-      <c r="G83" s="189"/>
-      <c r="H83" s="189"/>
-      <c r="I83" s="189"/>
-      <c r="J83" s="189"/>
-      <c r="K83" s="190"/>
+      <c r="F83" s="181"/>
+      <c r="G83" s="181"/>
+      <c r="H83" s="181"/>
+      <c r="I83" s="181"/>
+      <c r="J83" s="181"/>
+      <c r="K83" s="179"/>
       <c r="L83" s="152"/>
       <c r="M83" s="153"/>
     </row>
     <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="191" t="s">
+      <c r="E84" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="189"/>
-      <c r="G84" s="189"/>
-      <c r="H84" s="189"/>
-      <c r="I84" s="189"/>
-      <c r="J84" s="189"/>
-      <c r="K84" s="190"/>
+      <c r="F84" s="181"/>
+      <c r="G84" s="181"/>
+      <c r="H84" s="181"/>
+      <c r="I84" s="181"/>
+      <c r="J84" s="181"/>
+      <c r="K84" s="179"/>
       <c r="L84" s="154"/>
       <c r="M84" s="155"/>
     </row>
@@ -4279,15 +4157,15 @@
       <c r="M87" s="155"/>
     </row>
     <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="192" t="s">
+      <c r="E88" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="193"/>
-      <c r="G88" s="193"/>
-      <c r="H88" s="193"/>
-      <c r="I88" s="193"/>
-      <c r="J88" s="193"/>
-      <c r="K88" s="194"/>
+      <c r="F88" s="184"/>
+      <c r="G88" s="184"/>
+      <c r="H88" s="184"/>
+      <c r="I88" s="184"/>
+      <c r="J88" s="184"/>
+      <c r="K88" s="185"/>
       <c r="L88" s="154"/>
       <c r="M88" s="155"/>
     </row>
@@ -4319,10 +4197,10 @@
         <v>45674</v>
       </c>
       <c r="K90" s="155"/>
-      <c r="L90" s="195" t="s">
+      <c r="L90" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="196"/>
+      <c r="M90" s="187"/>
     </row>
     <row r="91" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E91" s="154" t="s">
@@ -4347,8 +4225,8 @@
       <c r="I92" s="157"/>
       <c r="J92" s="157"/>
       <c r="K92" s="155"/>
-      <c r="L92" s="197"/>
-      <c r="M92" s="196"/>
+      <c r="L92" s="188"/>
+      <c r="M92" s="187"/>
     </row>
     <row r="93" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E93" s="154" t="s">
@@ -4360,7 +4238,7 @@
       <c r="I93" s="157"/>
       <c r="J93" s="163">
         <f>J10</f>
-        <v>54674.091264000002</v>
+        <v>20640.604608000001</v>
       </c>
       <c r="K93" s="155"/>
       <c r="L93" s="154"/>
@@ -4376,7 +4254,7 @@
       <c r="I94" s="157"/>
       <c r="J94" s="163">
         <f>K10</f>
-        <v>33656.502048000002</v>
+        <v>0</v>
       </c>
       <c r="K94" s="155"/>
       <c r="L94" s="154"/>
@@ -4474,45 +4352,45 @@
       <c r="M102" s="166"/>
     </row>
     <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="198" t="s">
+      <c r="E103" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="199"/>
-      <c r="G103" s="199"/>
-      <c r="H103" s="199"/>
-      <c r="I103" s="199"/>
-      <c r="J103" s="200">
+      <c r="F103" s="177"/>
+      <c r="G103" s="177"/>
+      <c r="H103" s="177"/>
+      <c r="I103" s="177"/>
+      <c r="J103" s="178">
         <f>SUM(J93:J102)</f>
-        <v>88354.483312000011</v>
-      </c>
-      <c r="K103" s="190"/>
+        <v>20664.494608000001</v>
+      </c>
+      <c r="K103" s="179"/>
       <c r="L103" s="167"/>
       <c r="M103" s="168"/>
     </row>
     <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="188" t="s">
+      <c r="E108" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="189"/>
-      <c r="G108" s="189"/>
-      <c r="H108" s="189"/>
-      <c r="I108" s="189"/>
-      <c r="J108" s="189"/>
-      <c r="K108" s="190"/>
+      <c r="F108" s="181"/>
+      <c r="G108" s="181"/>
+      <c r="H108" s="181"/>
+      <c r="I108" s="181"/>
+      <c r="J108" s="181"/>
+      <c r="K108" s="179"/>
       <c r="L108" s="152"/>
       <c r="M108" s="153"/>
     </row>
     <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="191" t="s">
+      <c r="E109" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="189"/>
-      <c r="G109" s="189"/>
-      <c r="H109" s="189"/>
-      <c r="I109" s="189"/>
-      <c r="J109" s="189"/>
-      <c r="K109" s="190"/>
+      <c r="F109" s="181"/>
+      <c r="G109" s="181"/>
+      <c r="H109" s="181"/>
+      <c r="I109" s="181"/>
+      <c r="J109" s="181"/>
+      <c r="K109" s="179"/>
       <c r="L109" s="154"/>
       <c r="M109" s="155"/>
     </row>
@@ -4555,15 +4433,15 @@
       <c r="M112" s="155"/>
     </row>
     <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="192" t="s">
+      <c r="E113" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="193"/>
-      <c r="G113" s="193"/>
-      <c r="H113" s="193"/>
-      <c r="I113" s="193"/>
-      <c r="J113" s="193"/>
-      <c r="K113" s="194"/>
+      <c r="F113" s="184"/>
+      <c r="G113" s="184"/>
+      <c r="H113" s="184"/>
+      <c r="I113" s="184"/>
+      <c r="J113" s="184"/>
+      <c r="K113" s="185"/>
       <c r="L113" s="154"/>
       <c r="M113" s="155"/>
     </row>
@@ -4595,10 +4473,10 @@
         <v>45674</v>
       </c>
       <c r="K115" s="155"/>
-      <c r="L115" s="195" t="s">
+      <c r="L115" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="196"/>
+      <c r="M115" s="187"/>
     </row>
     <row r="116" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E116" s="154" t="s">
@@ -4623,8 +4501,8 @@
       <c r="I117" s="157"/>
       <c r="J117" s="157"/>
       <c r="K117" s="155"/>
-      <c r="L117" s="197"/>
-      <c r="M117" s="196"/>
+      <c r="L117" s="188"/>
+      <c r="M117" s="187"/>
     </row>
     <row r="118" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E118" s="154" t="s">
@@ -4636,7 +4514,7 @@
       <c r="I118" s="157"/>
       <c r="J118" s="163">
         <f>J5</f>
-        <v>60456.927839999997</v>
+        <v>22823.745480000005</v>
       </c>
       <c r="K118" s="155"/>
       <c r="L118" s="154"/>
@@ -4652,7 +4530,7 @@
       <c r="I119" s="157"/>
       <c r="J119" s="163">
         <f>K5</f>
-        <v>37216.324380000005</v>
+        <v>0</v>
       </c>
       <c r="K119" s="155"/>
       <c r="L119" s="154"/>
@@ -4751,50 +4629,26 @@
       <c r="M127" s="166"/>
     </row>
     <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="198" t="s">
+      <c r="E128" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="199"/>
-      <c r="G128" s="199"/>
-      <c r="H128" s="199"/>
-      <c r="I128" s="199"/>
-      <c r="J128" s="200">
+      <c r="F128" s="177"/>
+      <c r="G128" s="177"/>
+      <c r="H128" s="177"/>
+      <c r="I128" s="177"/>
+      <c r="J128" s="178">
         <f>SUM(J118:J127)</f>
-        <v>97620.912219999998</v>
-      </c>
-      <c r="K128" s="190"/>
+        <v>22771.405480000005</v>
+      </c>
+      <c r="K128" s="179"/>
       <c r="L128" s="167"/>
       <c r="M128" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E108:K108"/>
-    <mergeCell ref="E109:K109"/>
-    <mergeCell ref="E113:K113"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="E76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="E56:K56"/>
-    <mergeCell ref="E57:K57"/>
-    <mergeCell ref="E61:K61"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="E33:K33"/>
-    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="K3:K4"/>
@@ -4811,9 +4665,33 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="E76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E108:K108"/>
+    <mergeCell ref="E109:K109"/>
+    <mergeCell ref="E113:K113"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="E56:K56"/>
+    <mergeCell ref="E57:K57"/>
+    <mergeCell ref="E61:K61"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="E37:K37"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5370,11 +5248,11 @@
       <c r="D1" s="55">
         <v>50000</v>
       </c>
-      <c r="H1" s="205">
+      <c r="H1" s="207">
         <v>250000</v>
       </c>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
@@ -5438,13 +5316,13 @@
         <v>53</v>
       </c>
       <c r="K4" s="67"/>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="205" t="s">
         <v>60</v>
       </c>
       <c r="M4" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="201" t="s">
+      <c r="N4" s="203" t="s">
         <v>54</v>
       </c>
       <c r="P4" s="21"/>
@@ -5473,11 +5351,11 @@
         <v>59</v>
       </c>
       <c r="K5" s="57"/>
-      <c r="L5" s="204"/>
+      <c r="L5" s="206"/>
       <c r="M5" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="N5" s="202"/>
+      <c r="N5" s="204"/>
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -5956,7 +5834,7 @@
       <c r="D1" s="208"/>
       <c r="E1" s="208"/>
       <c r="F1" s="209" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G1" s="209"/>
       <c r="H1" s="209"/>
@@ -5980,14 +5858,14 @@
       <c r="L2" s="102"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="199" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="183"/>
-      <c r="C3" s="178" t="s">
+      <c r="B3" s="200"/>
+      <c r="C3" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="180" t="s">
+      <c r="D3" s="197" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -5996,50 +5874,50 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="178" t="s">
+      <c r="G3" s="189" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="178" t="s">
+      <c r="H3" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="176" t="s">
+      <c r="I3" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="180" t="s">
+      <c r="J3" s="197" t="s">
         <v>128</v>
       </c>
       <c r="K3" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="L3" s="206" t="s">
+      <c r="L3" s="211" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="184"/>
-      <c r="B4" s="185"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="181"/>
+      <c r="A4" s="201"/>
+      <c r="B4" s="202"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="198"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="179"/>
-      <c r="H4" s="179"/>
-      <c r="I4" s="177"/>
-      <c r="J4" s="181"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="196"/>
+      <c r="J4" s="198"/>
       <c r="K4" s="171" t="s">
         <v>129</v>
       </c>
-      <c r="L4" s="207"/>
+      <c r="L4" s="212"/>
     </row>
     <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="174">
+      <c r="A5" s="193">
         <v>1</v>
       </c>
-      <c r="B5" s="175"/>
+      <c r="B5" s="194"/>
       <c r="C5" s="110" t="s">
         <v>65</v>
       </c>
@@ -6076,10 +5954,10 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="174">
+      <c r="A6" s="193">
         <v>2</v>
       </c>
-      <c r="B6" s="175"/>
+      <c r="B6" s="194"/>
       <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
@@ -6118,10 +5996,10 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="174">
+      <c r="A7" s="193">
         <v>3</v>
       </c>
-      <c r="B7" s="175"/>
+      <c r="B7" s="194"/>
       <c r="C7" s="110" t="s">
         <v>66</v>
       </c>
@@ -6160,10 +6038,10 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="174">
+      <c r="A8" s="193">
         <v>4</v>
       </c>
-      <c r="B8" s="175"/>
+      <c r="B8" s="194"/>
       <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
@@ -6202,10 +6080,10 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="174">
+      <c r="A9" s="193">
         <v>5</v>
       </c>
-      <c r="B9" s="175"/>
+      <c r="B9" s="194"/>
       <c r="C9" s="110" t="s">
         <v>68</v>
       </c>
@@ -6244,10 +6122,10 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="174">
+      <c r="A10" s="193">
         <v>6</v>
       </c>
-      <c r="B10" s="175"/>
+      <c r="B10" s="194"/>
       <c r="C10" s="110" t="s">
         <v>69</v>
       </c>
@@ -6284,10 +6162,10 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="174">
+      <c r="A11" s="193">
         <v>7</v>
       </c>
-      <c r="B11" s="175"/>
+      <c r="B11" s="194"/>
       <c r="C11" s="110" t="s">
         <v>70</v>
       </c>
@@ -6324,10 +6202,10 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="174" t="s">
+      <c r="A12" s="193" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="175"/>
+      <c r="B12" s="194"/>
       <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -6365,10 +6243,10 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="174" t="s">
+      <c r="A13" s="193" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="175"/>
+      <c r="B13" s="194"/>
       <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6406,10 +6284,10 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="174" t="s">
+      <c r="A14" s="193" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="175"/>
+      <c r="B14" s="194"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6875,15 +6753,15 @@
     <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="188" t="s">
+      <c r="E32" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="189"/>
-      <c r="G32" s="189"/>
-      <c r="H32" s="189"/>
-      <c r="I32" s="189"/>
-      <c r="J32" s="189"/>
-      <c r="K32" s="190"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="179"/>
       <c r="L32" s="152"/>
       <c r="M32" s="153"/>
       <c r="N32"/>
@@ -6891,15 +6769,15 @@
     <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="191" t="s">
+      <c r="E33" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="189"/>
-      <c r="G33" s="189"/>
-      <c r="H33" s="189"/>
-      <c r="I33" s="189"/>
-      <c r="J33" s="189"/>
-      <c r="K33" s="190"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="179"/>
       <c r="L33" s="154"/>
       <c r="M33" s="155"/>
       <c r="N33"/>
@@ -6954,15 +6832,15 @@
     <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="192" t="s">
+      <c r="E37" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="193"/>
-      <c r="G37" s="193"/>
-      <c r="H37" s="193"/>
-      <c r="I37" s="193"/>
-      <c r="J37" s="193"/>
-      <c r="K37" s="194"/>
+      <c r="F37" s="184"/>
+      <c r="G37" s="184"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="184"/>
+      <c r="J37" s="184"/>
+      <c r="K37" s="185"/>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37"/>
@@ -7000,10 +6878,10 @@
         <v>45674</v>
       </c>
       <c r="K39" s="155"/>
-      <c r="L39" s="195" t="s">
+      <c r="L39" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="196"/>
+      <c r="M39" s="187"/>
       <c r="N39"/>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.25">
@@ -7034,8 +6912,8 @@
       <c r="I41" s="157"/>
       <c r="J41" s="157"/>
       <c r="K41" s="155"/>
-      <c r="L41" s="197"/>
-      <c r="M41" s="196"/>
+      <c r="L41" s="188"/>
+      <c r="M41" s="187"/>
       <c r="N41"/>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.25">
@@ -7200,18 +7078,18 @@
     <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="198" t="s">
+      <c r="E52" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="199"/>
-      <c r="G52" s="199"/>
-      <c r="H52" s="199"/>
-      <c r="I52" s="199"/>
-      <c r="J52" s="200">
+      <c r="F52" s="177"/>
+      <c r="G52" s="177"/>
+      <c r="H52" s="177"/>
+      <c r="I52" s="177"/>
+      <c r="J52" s="178">
         <f>SUM(J42:J51)</f>
         <v>99755.8</v>
       </c>
-      <c r="K52" s="190"/>
+      <c r="K52" s="179"/>
       <c r="L52" s="167"/>
       <c r="M52" s="168"/>
       <c r="N52"/>
@@ -7223,28 +7101,28 @@
     </row>
     <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="188" t="s">
+      <c r="E56" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="189"/>
-      <c r="G56" s="189"/>
-      <c r="H56" s="189"/>
-      <c r="I56" s="189"/>
-      <c r="J56" s="189"/>
-      <c r="K56" s="190"/>
+      <c r="F56" s="181"/>
+      <c r="G56" s="181"/>
+      <c r="H56" s="181"/>
+      <c r="I56" s="181"/>
+      <c r="J56" s="181"/>
+      <c r="K56" s="179"/>
       <c r="L56" s="152"/>
       <c r="M56" s="153"/>
     </row>
     <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="191" t="s">
+      <c r="E57" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="189"/>
-      <c r="G57" s="189"/>
-      <c r="H57" s="189"/>
-      <c r="I57" s="189"/>
-      <c r="J57" s="189"/>
-      <c r="K57" s="190"/>
+      <c r="F57" s="181"/>
+      <c r="G57" s="181"/>
+      <c r="H57" s="181"/>
+      <c r="I57" s="181"/>
+      <c r="J57" s="181"/>
+      <c r="K57" s="179"/>
       <c r="L57" s="154"/>
       <c r="M57" s="155"/>
     </row>
@@ -7287,15 +7165,15 @@
       <c r="M60" s="155"/>
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="192" t="s">
+      <c r="E61" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="193"/>
-      <c r="G61" s="193"/>
-      <c r="H61" s="193"/>
-      <c r="I61" s="193"/>
-      <c r="J61" s="193"/>
-      <c r="K61" s="194"/>
+      <c r="F61" s="184"/>
+      <c r="G61" s="184"/>
+      <c r="H61" s="184"/>
+      <c r="I61" s="184"/>
+      <c r="J61" s="184"/>
+      <c r="K61" s="185"/>
       <c r="L61" s="154"/>
       <c r="M61" s="155"/>
     </row>
@@ -7327,10 +7205,10 @@
         <v>45674</v>
       </c>
       <c r="K63" s="155"/>
-      <c r="L63" s="195" t="s">
+      <c r="L63" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="196"/>
+      <c r="M63" s="187"/>
     </row>
     <row r="64" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E64" s="154" t="s">
@@ -7355,8 +7233,8 @@
       <c r="I65" s="157"/>
       <c r="J65" s="157"/>
       <c r="K65" s="155"/>
-      <c r="L65" s="197"/>
-      <c r="M65" s="196"/>
+      <c r="L65" s="188"/>
+      <c r="M65" s="187"/>
     </row>
     <row r="66" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E66" s="154" t="s">
@@ -7483,45 +7361,45 @@
       <c r="M75" s="166"/>
     </row>
     <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="198" t="s">
+      <c r="E76" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="199"/>
-      <c r="G76" s="199"/>
-      <c r="H76" s="199"/>
-      <c r="I76" s="199"/>
-      <c r="J76" s="200">
+      <c r="F76" s="177"/>
+      <c r="G76" s="177"/>
+      <c r="H76" s="177"/>
+      <c r="I76" s="177"/>
+      <c r="J76" s="178">
         <f>SUM(J66:J75)</f>
         <v>118000</v>
       </c>
-      <c r="K76" s="190"/>
+      <c r="K76" s="179"/>
       <c r="L76" s="167"/>
       <c r="M76" s="168"/>
     </row>
     <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="188" t="s">
+      <c r="E83" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="189"/>
-      <c r="G83" s="189"/>
-      <c r="H83" s="189"/>
-      <c r="I83" s="189"/>
-      <c r="J83" s="189"/>
-      <c r="K83" s="190"/>
+      <c r="F83" s="181"/>
+      <c r="G83" s="181"/>
+      <c r="H83" s="181"/>
+      <c r="I83" s="181"/>
+      <c r="J83" s="181"/>
+      <c r="K83" s="179"/>
       <c r="L83" s="152"/>
       <c r="M83" s="153"/>
     </row>
     <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="191" t="s">
+      <c r="E84" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="189"/>
-      <c r="G84" s="189"/>
-      <c r="H84" s="189"/>
-      <c r="I84" s="189"/>
-      <c r="J84" s="189"/>
-      <c r="K84" s="190"/>
+      <c r="F84" s="181"/>
+      <c r="G84" s="181"/>
+      <c r="H84" s="181"/>
+      <c r="I84" s="181"/>
+      <c r="J84" s="181"/>
+      <c r="K84" s="179"/>
       <c r="L84" s="154"/>
       <c r="M84" s="155"/>
     </row>
@@ -7564,15 +7442,15 @@
       <c r="M87" s="155"/>
     </row>
     <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="192" t="s">
+      <c r="E88" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="193"/>
-      <c r="G88" s="193"/>
-      <c r="H88" s="193"/>
-      <c r="I88" s="193"/>
-      <c r="J88" s="193"/>
-      <c r="K88" s="194"/>
+      <c r="F88" s="184"/>
+      <c r="G88" s="184"/>
+      <c r="H88" s="184"/>
+      <c r="I88" s="184"/>
+      <c r="J88" s="184"/>
+      <c r="K88" s="185"/>
       <c r="L88" s="154"/>
       <c r="M88" s="155"/>
     </row>
@@ -7604,10 +7482,10 @@
         <v>45674</v>
       </c>
       <c r="K90" s="155"/>
-      <c r="L90" s="195" t="s">
+      <c r="L90" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="196"/>
+      <c r="M90" s="187"/>
     </row>
     <row r="91" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E91" s="154" t="s">
@@ -7632,8 +7510,8 @@
       <c r="I92" s="157"/>
       <c r="J92" s="157"/>
       <c r="K92" s="155"/>
-      <c r="L92" s="197"/>
-      <c r="M92" s="196"/>
+      <c r="L92" s="188"/>
+      <c r="M92" s="187"/>
     </row>
     <row r="93" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E93" s="154" t="s">
@@ -7759,45 +7637,45 @@
       <c r="M102" s="166"/>
     </row>
     <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="198" t="s">
+      <c r="E103" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="199"/>
-      <c r="G103" s="199"/>
-      <c r="H103" s="199"/>
-      <c r="I103" s="199"/>
-      <c r="J103" s="200">
+      <c r="F103" s="177"/>
+      <c r="G103" s="177"/>
+      <c r="H103" s="177"/>
+      <c r="I103" s="177"/>
+      <c r="J103" s="178">
         <f>SUM(J93:J102)</f>
         <v>99863.89</v>
       </c>
-      <c r="K103" s="190"/>
+      <c r="K103" s="179"/>
       <c r="L103" s="167"/>
       <c r="M103" s="168"/>
     </row>
     <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="188" t="s">
+      <c r="E108" s="180" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="189"/>
-      <c r="G108" s="189"/>
-      <c r="H108" s="189"/>
-      <c r="I108" s="189"/>
-      <c r="J108" s="189"/>
-      <c r="K108" s="190"/>
+      <c r="F108" s="181"/>
+      <c r="G108" s="181"/>
+      <c r="H108" s="181"/>
+      <c r="I108" s="181"/>
+      <c r="J108" s="181"/>
+      <c r="K108" s="179"/>
       <c r="L108" s="152"/>
       <c r="M108" s="153"/>
     </row>
     <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="191" t="s">
+      <c r="E109" s="182" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="189"/>
-      <c r="G109" s="189"/>
-      <c r="H109" s="189"/>
-      <c r="I109" s="189"/>
-      <c r="J109" s="189"/>
-      <c r="K109" s="190"/>
+      <c r="F109" s="181"/>
+      <c r="G109" s="181"/>
+      <c r="H109" s="181"/>
+      <c r="I109" s="181"/>
+      <c r="J109" s="181"/>
+      <c r="K109" s="179"/>
       <c r="L109" s="154"/>
       <c r="M109" s="155"/>
     </row>
@@ -7840,15 +7718,15 @@
       <c r="M112" s="155"/>
     </row>
     <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="192" t="s">
+      <c r="E113" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="193"/>
-      <c r="G113" s="193"/>
-      <c r="H113" s="193"/>
-      <c r="I113" s="193"/>
-      <c r="J113" s="193"/>
-      <c r="K113" s="194"/>
+      <c r="F113" s="184"/>
+      <c r="G113" s="184"/>
+      <c r="H113" s="184"/>
+      <c r="I113" s="184"/>
+      <c r="J113" s="184"/>
+      <c r="K113" s="185"/>
       <c r="L113" s="154"/>
       <c r="M113" s="155"/>
     </row>
@@ -7880,10 +7758,10 @@
         <v>45674</v>
       </c>
       <c r="K115" s="155"/>
-      <c r="L115" s="195" t="s">
+      <c r="L115" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="196"/>
+      <c r="M115" s="187"/>
     </row>
     <row r="116" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E116" s="154" t="s">
@@ -7908,8 +7786,8 @@
       <c r="I117" s="157"/>
       <c r="J117" s="157"/>
       <c r="K117" s="155"/>
-      <c r="L117" s="197"/>
-      <c r="M117" s="196"/>
+      <c r="L117" s="188"/>
+      <c r="M117" s="187"/>
     </row>
     <row r="118" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E118" s="154" t="s">
@@ -8036,57 +7914,23 @@
       <c r="M127" s="166"/>
     </row>
     <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="198" t="s">
+      <c r="E128" s="176" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="199"/>
-      <c r="G128" s="199"/>
-      <c r="H128" s="199"/>
-      <c r="I128" s="199"/>
-      <c r="J128" s="200">
+      <c r="F128" s="177"/>
+      <c r="G128" s="177"/>
+      <c r="H128" s="177"/>
+      <c r="I128" s="177"/>
+      <c r="J128" s="178">
         <f>SUM(J118:J127)</f>
         <v>110347.66</v>
       </c>
-      <c r="K128" s="190"/>
+      <c r="K128" s="179"/>
       <c r="L128" s="167"/>
       <c r="M128" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="E108:K108"/>
     <mergeCell ref="E109:K109"/>
@@ -8103,6 +7947,40 @@
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="E52:I52"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/PATXOT 512/Septiembre/PATXOT 521 Septiembre.xlsx
+++ b/PATXOT 512/Septiembre/PATXOT 521 Septiembre.xlsx
@@ -5,32 +5,34 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PATXOT 512\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F43BF9B-6BDA-412C-863E-4C84D8004346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4312CFA0-E50D-43C3-92C3-79BDA32CC269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
-    <sheet name="edesur" sheetId="5" r:id="rId3"/>
-    <sheet name="eXTR" sheetId="4" r:id="rId4"/>
-    <sheet name="PRORRATEO EXPRESS" sheetId="6" r:id="rId5"/>
+    <sheet name="prorrateo 2" sheetId="7" r:id="rId3"/>
+    <sheet name="edesur" sheetId="5" r:id="rId4"/>
+    <sheet name="eXTR" sheetId="4" r:id="rId5"/>
+    <sheet name="PRORRATEO EXPRESS" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$41</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">edesur!$A$1:$H$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">edesur!$A$1:$H$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'PRORRATEO EXPRESS'!$A$1:$L$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'prorrateo 2'!$A$1:$L$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'PRORRATEO EXPRESS'!$A$1:$L$16</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="141">
   <si>
     <t>UF</t>
   </si>
@@ -441,13 +443,25 @@
   </si>
   <si>
     <t>Edesur - septiembre</t>
+  </si>
+  <si>
+    <t>Partida nro. 121216000</t>
+  </si>
+  <si>
+    <t>Partida nro. 121216000 - 2022 al 2024</t>
+  </si>
+  <si>
+    <t>Partida nro. 12126001</t>
+  </si>
+  <si>
+    <t>Partida nro. 12126001 - 2022 al 2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
@@ -455,8 +469,9 @@
     <numFmt numFmtId="167" formatCode="d/m"/>
     <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="169" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -624,6 +639,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1452,7 +1474,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1728,8 +1750,52 @@
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1749,52 +1815,8 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1811,6 +1833,12 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1820,12 +1848,23 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2196,16 +2235,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>21</v>
       </c>
@@ -2213,66 +2252,66 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="169" t="s">
         <v>132</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="86" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="75"/>
       <c r="C16" s="11"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="75" t="s">
         <v>133</v>
       </c>
@@ -2285,7 +2324,7 @@
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="88"/>
       <c r="B18" s="89"/>
       <c r="C18" s="60">
@@ -2293,14 +2332,14 @@
         <v>91854.86</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="86" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="87"/>
       <c r="C19" s="90"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="75" t="s">
         <v>134</v>
       </c>
@@ -2310,7 +2349,7 @@
       </c>
       <c r="F20" s="22"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="75" t="s">
         <v>135</v>
       </c>
@@ -2320,7 +2359,7 @@
       </c>
       <c r="F21" s="22"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="75" t="s">
         <v>124</v>
       </c>
@@ -2330,7 +2369,7 @@
       <c r="E22" s="14"/>
       <c r="F22" s="22"/>
     </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="88"/>
       <c r="B23" s="89"/>
       <c r="C23" s="60">
@@ -2339,7 +2378,7 @@
       </c>
       <c r="F23" s="22"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="79" t="s">
         <v>78</v>
       </c>
@@ -2350,40 +2389,40 @@
       </c>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C25" s="61"/>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="61"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="75"/>
       <c r="B27" s="75"/>
       <c r="C27" s="84"/>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="75"/>
       <c r="B28" s="75"/>
       <c r="C28" s="85"/>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="75"/>
       <c r="B29" s="75"/>
       <c r="C29" s="85"/>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C30" s="63"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>40</v>
       </c>
@@ -2394,7 +2433,7 @@
       </c>
       <c r="E31" s="14"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="34" t="s">
         <v>15</v>
       </c>
@@ -2404,15 +2443,15 @@
         <v>165389.46000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="146" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="147"/>
       <c r="C35" s="148"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="144" t="s">
         <v>10</v>
       </c>
@@ -2423,7 +2462,7 @@
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2434,7 +2473,7 @@
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -2444,7 +2483,7 @@
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -2453,7 +2492,7 @@
         <v>-165389.46000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="36" t="s">
         <v>16</v>
       </c>
@@ -2464,23 +2503,23 @@
       </c>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="19"/>
       <c r="B41" s="18"/>
       <c r="C41" s="20"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="19"/>
       <c r="B42" s="18"/>
       <c r="C42" s="20"/>
       <c r="F42" s="94"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="19"/>
       <c r="B43" s="18"/>
       <c r="C43" s="20"/>
     </row>
-    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="73" t="s">
         <v>57</v>
       </c>
@@ -2489,7 +2528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="75" t="s">
         <v>63</v>
       </c>
@@ -2499,17 +2538,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="75"/>
       <c r="B46" s="75"/>
       <c r="C46" s="82"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="75"/>
       <c r="B47" s="75"/>
       <c r="C47" s="83"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="79" t="s">
         <v>4</v>
       </c>
@@ -2519,22 +2558,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="18"/>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="18"/>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="18"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="18"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -2556,37 +2595,37 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="21"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="52" t="s">
         <v>48</v>
       </c>
       <c r="E1" s="14">
         <v>165389.46000000002</v>
       </c>
-      <c r="H1" s="175" t="s">
+      <c r="H1" s="202" t="s">
         <v>131</v>
       </c>
-      <c r="I1" s="175"/>
+      <c r="I1" s="202"/>
       <c r="J1" s="14"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="97">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
@@ -2603,15 +2642,15 @@
       <c r="K2" s="101"/>
       <c r="L2" s="102"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="199" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="177" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="200"/>
-      <c r="C3" s="189" t="s">
+      <c r="B3" s="178"/>
+      <c r="C3" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="197" t="s">
+      <c r="D3" s="175" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2620,52 +2659,52 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="189" t="s">
+      <c r="G3" s="186" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="195" t="s">
+      <c r="I3" s="190" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="191" t="s">
+      <c r="J3" s="188" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="189" t="s">
+      <c r="K3" s="186" t="s">
         <v>42</v>
       </c>
       <c r="L3" s="45" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="201"/>
-      <c r="B4" s="202"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="198"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="179"/>
+      <c r="B4" s="180"/>
+      <c r="C4" s="187"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="190"/>
+      <c r="G4" s="187"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="196"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="190"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="189"/>
+      <c r="K4" s="187"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="193">
+    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="181">
         <v>1</v>
       </c>
-      <c r="B5" s="194"/>
+      <c r="B5" s="182"/>
       <c r="C5" s="110" t="s">
         <v>65</v>
       </c>
@@ -2698,11 +2737,11 @@
         <v>66016.406332382612</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="193">
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="181">
         <v>2</v>
       </c>
-      <c r="B6" s="194"/>
+      <c r="B6" s="182"/>
       <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
@@ -2737,11 +2776,11 @@
         <v>57228.795481850429</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="193">
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
         <v>3</v>
       </c>
-      <c r="B7" s="194"/>
+      <c r="B7" s="182"/>
       <c r="C7" s="110" t="s">
         <v>66</v>
       </c>
@@ -2776,11 +2815,11 @@
         <v>60017.321216528711</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="193">
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="181">
         <v>4</v>
       </c>
-      <c r="B8" s="194"/>
+      <c r="B8" s="182"/>
       <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
@@ -2815,11 +2854,11 @@
         <v>70907.619939826094</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="193">
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="181">
         <v>5</v>
       </c>
-      <c r="B9" s="194"/>
+      <c r="B9" s="182"/>
       <c r="C9" s="110" t="s">
         <v>68</v>
       </c>
@@ -2854,11 +2893,11 @@
         <v>59120.864767624356</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="193">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="181">
         <v>6</v>
       </c>
-      <c r="B10" s="194"/>
+      <c r="B10" s="182"/>
       <c r="C10" s="110" t="s">
         <v>69</v>
       </c>
@@ -2891,11 +2930,11 @@
         <v>59466.18976478609</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="193">
+    <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="181">
         <v>7</v>
       </c>
-      <c r="B11" s="194"/>
+      <c r="B11" s="182"/>
       <c r="C11" s="110" t="s">
         <v>70</v>
       </c>
@@ -2928,11 +2967,11 @@
         <v>87074.54727204176</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="193" t="s">
+    <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="181" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="194"/>
+      <c r="B12" s="182"/>
       <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -2966,11 +3005,11 @@
         <v>6267.7014636800004</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="193" t="s">
+    <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="181" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="194"/>
+      <c r="B13" s="182"/>
       <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3004,11 +3043,11 @@
         <v>6174.1536806399999</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="193" t="s">
+    <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="181" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="194"/>
+      <c r="B14" s="182"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3042,7 +3081,7 @@
         <v>6174.1536806399999</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="104" t="s">
         <v>11</v>
       </c>
@@ -3079,7 +3118,7 @@
         <v>478447.75360000005</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52" t="s">
         <v>49</v>
       </c>
@@ -3087,7 +3126,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>51</v>
       </c>
@@ -3105,7 +3144,7 @@
       <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -3137,7 +3176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3163,7 +3202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -3197,7 +3236,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -3231,7 +3270,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -3266,7 +3305,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -3297,7 +3336,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -3328,7 +3367,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -3359,7 +3398,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -3393,7 +3432,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -3427,7 +3466,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -3460,44 +3499,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="180" t="s">
+      <c r="E32" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="181"/>
-      <c r="I32" s="181"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="179"/>
+      <c r="F32" s="197"/>
+      <c r="G32" s="197"/>
+      <c r="H32" s="197"/>
+      <c r="I32" s="197"/>
+      <c r="J32" s="197"/>
+      <c r="K32" s="195"/>
       <c r="L32" s="152"/>
       <c r="M32" s="153"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="182" t="s">
+      <c r="E33" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="181"/>
-      <c r="G33" s="181"/>
-      <c r="H33" s="181"/>
-      <c r="I33" s="181"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="179"/>
+      <c r="F33" s="197"/>
+      <c r="G33" s="197"/>
+      <c r="H33" s="197"/>
+      <c r="I33" s="197"/>
+      <c r="J33" s="197"/>
+      <c r="K33" s="195"/>
       <c r="L33" s="154"/>
       <c r="M33" s="155"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="152"/>
@@ -3514,7 +3553,7 @@
       <c r="M34" s="155"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="154" t="s">
@@ -3530,7 +3569,7 @@
       <c r="M35" s="155"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="158"/>
@@ -3544,23 +3583,23 @@
       <c r="M36" s="155"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="183" t="s">
+      <c r="E37" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="185"/>
+      <c r="F37" s="200"/>
+      <c r="G37" s="200"/>
+      <c r="H37" s="200"/>
+      <c r="I37" s="200"/>
+      <c r="J37" s="200"/>
+      <c r="K37" s="201"/>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="154"/>
@@ -3574,7 +3613,7 @@
       <c r="M38" s="155"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="154" t="s">
@@ -3593,13 +3632,13 @@
         <v>45674</v>
       </c>
       <c r="K39" s="155"/>
-      <c r="L39" s="186" t="s">
+      <c r="L39" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="187"/>
+      <c r="M39" s="184"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="154" t="s">
@@ -3617,7 +3656,7 @@
       <c r="M40" s="155"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="154"/>
@@ -3627,11 +3666,11 @@
       <c r="I41" s="157"/>
       <c r="J41" s="157"/>
       <c r="K41" s="155"/>
-      <c r="L41" s="188"/>
-      <c r="M41" s="187"/>
+      <c r="L41" s="185"/>
+      <c r="M41" s="184"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="154" t="s">
@@ -3650,7 +3689,7 @@
       <c r="M42" s="155"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="164" t="s">
@@ -3669,7 +3708,7 @@
       <c r="M43" s="155"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="164" t="s">
@@ -3688,7 +3727,7 @@
       <c r="M44" s="155"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="164"/>
@@ -3702,7 +3741,7 @@
       <c r="M45" s="155"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="164"/>
@@ -3716,7 +3755,7 @@
       <c r="M46" s="155"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="157"/>
@@ -3729,7 +3768,7 @@
       <c r="M47" s="155"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="164"/>
@@ -3743,7 +3782,7 @@
       <c r="M48" s="155"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="154"/>
@@ -3757,7 +3796,7 @@
       <c r="M49" s="155"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="154" t="s">
@@ -3776,7 +3815,7 @@
       <c r="M50" s="155"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="154"/>
@@ -3790,58 +3829,58 @@
       <c r="M51" s="166"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="176" t="s">
+      <c r="E52" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="177"/>
-      <c r="G52" s="177"/>
-      <c r="H52" s="177"/>
-      <c r="I52" s="177"/>
-      <c r="J52" s="178">
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="194">
         <f>SUM(J42:J51)</f>
         <v>60093.121216528714</v>
       </c>
-      <c r="K52" s="179"/>
+      <c r="K52" s="195"/>
       <c r="L52" s="167"/>
       <c r="M52" s="168"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="180" t="s">
+    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E56" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="181"/>
-      <c r="G56" s="181"/>
-      <c r="H56" s="181"/>
-      <c r="I56" s="181"/>
-      <c r="J56" s="181"/>
-      <c r="K56" s="179"/>
+      <c r="F56" s="197"/>
+      <c r="G56" s="197"/>
+      <c r="H56" s="197"/>
+      <c r="I56" s="197"/>
+      <c r="J56" s="197"/>
+      <c r="K56" s="195"/>
       <c r="L56" s="152"/>
       <c r="M56" s="153"/>
     </row>
-    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="182" t="s">
+    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E57" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="181"/>
-      <c r="G57" s="181"/>
-      <c r="H57" s="181"/>
-      <c r="I57" s="181"/>
-      <c r="J57" s="181"/>
-      <c r="K57" s="179"/>
+      <c r="F57" s="197"/>
+      <c r="G57" s="197"/>
+      <c r="H57" s="197"/>
+      <c r="I57" s="197"/>
+      <c r="J57" s="197"/>
+      <c r="K57" s="195"/>
       <c r="L57" s="154"/>
       <c r="M57" s="155"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E58" s="152"/>
       <c r="F58" s="156"/>
       <c r="G58" s="156"/>
@@ -3855,7 +3894,7 @@
       <c r="L58" s="154"/>
       <c r="M58" s="155"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E59" s="154" t="s">
         <v>113</v>
       </c>
@@ -3868,7 +3907,7 @@
       <c r="L59" s="154"/>
       <c r="M59" s="155"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E60" s="158"/>
       <c r="F60" s="159"/>
       <c r="G60" s="159"/>
@@ -3879,20 +3918,20 @@
       <c r="L60" s="154"/>
       <c r="M60" s="155"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="183" t="s">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E61" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="184"/>
-      <c r="G61" s="184"/>
-      <c r="H61" s="184"/>
-      <c r="I61" s="184"/>
-      <c r="J61" s="184"/>
-      <c r="K61" s="185"/>
+      <c r="F61" s="200"/>
+      <c r="G61" s="200"/>
+      <c r="H61" s="200"/>
+      <c r="I61" s="200"/>
+      <c r="J61" s="200"/>
+      <c r="K61" s="201"/>
       <c r="L61" s="154"/>
       <c r="M61" s="155"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E62" s="154"/>
       <c r="F62" s="157"/>
       <c r="G62" s="157"/>
@@ -3903,7 +3942,7 @@
       <c r="L62" s="154"/>
       <c r="M62" s="155"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E63" s="154" t="s">
         <v>114</v>
       </c>
@@ -3920,12 +3959,12 @@
         <v>45674</v>
       </c>
       <c r="K63" s="155"/>
-      <c r="L63" s="186" t="s">
+      <c r="L63" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="187"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="M63" s="184"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E64" s="154" t="s">
         <v>117</v>
       </c>
@@ -3940,7 +3979,7 @@
       <c r="L64" s="154"/>
       <c r="M64" s="155"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E65" s="154"/>
       <c r="F65" s="157"/>
       <c r="G65" s="157"/>
@@ -3948,10 +3987,10 @@
       <c r="I65" s="157"/>
       <c r="J65" s="157"/>
       <c r="K65" s="155"/>
-      <c r="L65" s="188"/>
-      <c r="M65" s="187"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L65" s="185"/>
+      <c r="M65" s="184"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E66" s="154" t="s">
         <v>48</v>
       </c>
@@ -3967,7 +4006,7 @@
       <c r="L66" s="154"/>
       <c r="M66" s="155"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E67" s="164" t="s">
         <v>118</v>
       </c>
@@ -3983,7 +4022,7 @@
       <c r="L67" s="154"/>
       <c r="M67" s="155"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E68" s="164" t="s">
         <v>120</v>
       </c>
@@ -3999,7 +4038,7 @@
       <c r="L68" s="154"/>
       <c r="M68" s="155"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E69" s="164"/>
       <c r="F69" s="157"/>
       <c r="G69" s="157"/>
@@ -4010,7 +4049,7 @@
       <c r="L69" s="154"/>
       <c r="M69" s="155"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E70" s="164"/>
       <c r="F70" s="157"/>
       <c r="G70" s="157"/>
@@ -4021,7 +4060,7 @@
       <c r="L70" s="154"/>
       <c r="M70" s="155"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="F71" s="157"/>
       <c r="G71" s="157"/>
       <c r="H71" s="157"/>
@@ -4031,7 +4070,7 @@
       <c r="L71" s="154"/>
       <c r="M71" s="155"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E72" s="164"/>
       <c r="F72" s="157"/>
       <c r="G72" s="157"/>
@@ -4042,7 +4081,7 @@
       <c r="L72" s="154"/>
       <c r="M72" s="155"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E73" s="154"/>
       <c r="F73" s="157"/>
       <c r="G73" s="157"/>
@@ -4053,7 +4092,7 @@
       <c r="L73" s="154"/>
       <c r="M73" s="155"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E74" s="154"/>
       <c r="F74" s="157"/>
       <c r="G74" s="157"/>
@@ -4064,7 +4103,7 @@
       <c r="L74" s="154"/>
       <c r="M74" s="155"/>
     </row>
-    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E75" s="154"/>
       <c r="F75" s="157"/>
       <c r="G75" s="157"/>
@@ -4075,50 +4114,50 @@
       <c r="L75" s="165"/>
       <c r="M75" s="166"/>
     </row>
-    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="176" t="s">
+    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E76" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="177"/>
-      <c r="G76" s="177"/>
-      <c r="H76" s="177"/>
-      <c r="I76" s="177"/>
-      <c r="J76" s="178">
+      <c r="F76" s="193"/>
+      <c r="G76" s="193"/>
+      <c r="H76" s="193"/>
+      <c r="I76" s="193"/>
+      <c r="J76" s="194">
         <f>SUM(J66:J75)</f>
         <v>24394.945350000002</v>
       </c>
-      <c r="K76" s="179"/>
+      <c r="K76" s="195"/>
       <c r="L76" s="167"/>
       <c r="M76" s="168"/>
     </row>
-    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="180" t="s">
+    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E83" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="181"/>
-      <c r="G83" s="181"/>
-      <c r="H83" s="181"/>
-      <c r="I83" s="181"/>
-      <c r="J83" s="181"/>
-      <c r="K83" s="179"/>
+      <c r="F83" s="197"/>
+      <c r="G83" s="197"/>
+      <c r="H83" s="197"/>
+      <c r="I83" s="197"/>
+      <c r="J83" s="197"/>
+      <c r="K83" s="195"/>
       <c r="L83" s="152"/>
       <c r="M83" s="153"/>
     </row>
-    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="182" t="s">
+    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E84" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="181"/>
-      <c r="G84" s="181"/>
-      <c r="H84" s="181"/>
-      <c r="I84" s="181"/>
-      <c r="J84" s="181"/>
-      <c r="K84" s="179"/>
+      <c r="F84" s="197"/>
+      <c r="G84" s="197"/>
+      <c r="H84" s="197"/>
+      <c r="I84" s="197"/>
+      <c r="J84" s="197"/>
+      <c r="K84" s="195"/>
       <c r="L84" s="154"/>
       <c r="M84" s="155"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E85" s="152"/>
       <c r="F85" s="156"/>
       <c r="G85" s="156"/>
@@ -4132,7 +4171,7 @@
       <c r="L85" s="154"/>
       <c r="M85" s="155"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E86" s="154" t="s">
         <v>113</v>
       </c>
@@ -4145,7 +4184,7 @@
       <c r="L86" s="154"/>
       <c r="M86" s="155"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E87" s="158"/>
       <c r="F87" s="159"/>
       <c r="G87" s="159"/>
@@ -4156,20 +4195,20 @@
       <c r="L87" s="154"/>
       <c r="M87" s="155"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="183" t="s">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E88" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="184"/>
-      <c r="G88" s="184"/>
-      <c r="H88" s="184"/>
-      <c r="I88" s="184"/>
-      <c r="J88" s="184"/>
-      <c r="K88" s="185"/>
+      <c r="F88" s="200"/>
+      <c r="G88" s="200"/>
+      <c r="H88" s="200"/>
+      <c r="I88" s="200"/>
+      <c r="J88" s="200"/>
+      <c r="K88" s="201"/>
       <c r="L88" s="154"/>
       <c r="M88" s="155"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E89" s="154"/>
       <c r="F89" s="157"/>
       <c r="G89" s="157"/>
@@ -4180,7 +4219,7 @@
       <c r="L89" s="154"/>
       <c r="M89" s="155"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E90" s="154" t="s">
         <v>114</v>
       </c>
@@ -4197,12 +4236,12 @@
         <v>45674</v>
       </c>
       <c r="K90" s="155"/>
-      <c r="L90" s="186" t="s">
+      <c r="L90" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="187"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="M90" s="184"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E91" s="154" t="s">
         <v>117</v>
       </c>
@@ -4217,7 +4256,7 @@
       <c r="L91" s="154"/>
       <c r="M91" s="155"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E92" s="154"/>
       <c r="F92" s="157"/>
       <c r="G92" s="157"/>
@@ -4225,10 +4264,10 @@
       <c r="I92" s="157"/>
       <c r="J92" s="157"/>
       <c r="K92" s="155"/>
-      <c r="L92" s="188"/>
-      <c r="M92" s="187"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L92" s="185"/>
+      <c r="M92" s="184"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E93" s="154" t="s">
         <v>48</v>
       </c>
@@ -4244,7 +4283,7 @@
       <c r="L93" s="154"/>
       <c r="M93" s="155"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E94" s="164" t="s">
         <v>118</v>
       </c>
@@ -4260,7 +4299,7 @@
       <c r="L94" s="154"/>
       <c r="M94" s="155"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E95" s="164" t="s">
         <v>121</v>
       </c>
@@ -4275,7 +4314,7 @@
       <c r="L95" s="154"/>
       <c r="M95" s="155"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E96" s="164"/>
       <c r="F96" s="157"/>
       <c r="G96" s="157"/>
@@ -4286,7 +4325,7 @@
       <c r="L96" s="154"/>
       <c r="M96" s="155"/>
     </row>
-    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E97" s="164"/>
       <c r="F97" s="157"/>
       <c r="G97" s="157"/>
@@ -4297,7 +4336,7 @@
       <c r="L97" s="154"/>
       <c r="M97" s="155"/>
     </row>
-    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F98" s="157"/>
       <c r="G98" s="157"/>
       <c r="H98" s="157"/>
@@ -4307,7 +4346,7 @@
       <c r="L98" s="154"/>
       <c r="M98" s="155"/>
     </row>
-    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E99" s="164"/>
       <c r="F99" s="157"/>
       <c r="G99" s="157"/>
@@ -4318,7 +4357,7 @@
       <c r="L99" s="154"/>
       <c r="M99" s="155"/>
     </row>
-    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E100" s="154"/>
       <c r="F100" s="157"/>
       <c r="G100" s="157"/>
@@ -4329,7 +4368,7 @@
       <c r="L100" s="154"/>
       <c r="M100" s="155"/>
     </row>
-    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E101" s="154"/>
       <c r="F101" s="157"/>
       <c r="G101" s="157"/>
@@ -4340,7 +4379,7 @@
       <c r="L101" s="154"/>
       <c r="M101" s="155"/>
     </row>
-    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E102" s="154"/>
       <c r="F102" s="157"/>
       <c r="G102" s="157"/>
@@ -4351,50 +4390,50 @@
       <c r="L102" s="165"/>
       <c r="M102" s="166"/>
     </row>
-    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="176" t="s">
+    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E103" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="177"/>
-      <c r="G103" s="177"/>
-      <c r="H103" s="177"/>
-      <c r="I103" s="177"/>
-      <c r="J103" s="178">
+      <c r="F103" s="193"/>
+      <c r="G103" s="193"/>
+      <c r="H103" s="193"/>
+      <c r="I103" s="193"/>
+      <c r="J103" s="194">
         <f>SUM(J93:J102)</f>
         <v>20664.494608000001</v>
       </c>
-      <c r="K103" s="179"/>
+      <c r="K103" s="195"/>
       <c r="L103" s="167"/>
       <c r="M103" s="168"/>
     </row>
-    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="180" t="s">
+    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E108" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="181"/>
-      <c r="G108" s="181"/>
-      <c r="H108" s="181"/>
-      <c r="I108" s="181"/>
-      <c r="J108" s="181"/>
-      <c r="K108" s="179"/>
+      <c r="F108" s="197"/>
+      <c r="G108" s="197"/>
+      <c r="H108" s="197"/>
+      <c r="I108" s="197"/>
+      <c r="J108" s="197"/>
+      <c r="K108" s="195"/>
       <c r="L108" s="152"/>
       <c r="M108" s="153"/>
     </row>
-    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="182" t="s">
+    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E109" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="181"/>
-      <c r="G109" s="181"/>
-      <c r="H109" s="181"/>
-      <c r="I109" s="181"/>
-      <c r="J109" s="181"/>
-      <c r="K109" s="179"/>
+      <c r="F109" s="197"/>
+      <c r="G109" s="197"/>
+      <c r="H109" s="197"/>
+      <c r="I109" s="197"/>
+      <c r="J109" s="197"/>
+      <c r="K109" s="195"/>
       <c r="L109" s="154"/>
       <c r="M109" s="155"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E110" s="152"/>
       <c r="F110" s="156"/>
       <c r="G110" s="156"/>
@@ -4408,7 +4447,7 @@
       <c r="L110" s="154"/>
       <c r="M110" s="155"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E111" s="154" t="s">
         <v>113</v>
       </c>
@@ -4421,7 +4460,7 @@
       <c r="L111" s="154"/>
       <c r="M111" s="155"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E112" s="158"/>
       <c r="F112" s="159"/>
       <c r="G112" s="159"/>
@@ -4432,20 +4471,20 @@
       <c r="L112" s="154"/>
       <c r="M112" s="155"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="183" t="s">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E113" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="184"/>
-      <c r="G113" s="184"/>
-      <c r="H113" s="184"/>
-      <c r="I113" s="184"/>
-      <c r="J113" s="184"/>
-      <c r="K113" s="185"/>
+      <c r="F113" s="200"/>
+      <c r="G113" s="200"/>
+      <c r="H113" s="200"/>
+      <c r="I113" s="200"/>
+      <c r="J113" s="200"/>
+      <c r="K113" s="201"/>
       <c r="L113" s="154"/>
       <c r="M113" s="155"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E114" s="154"/>
       <c r="F114" s="157"/>
       <c r="G114" s="157"/>
@@ -4456,7 +4495,7 @@
       <c r="L114" s="154"/>
       <c r="M114" s="155"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E115" s="154" t="s">
         <v>114</v>
       </c>
@@ -4473,12 +4512,12 @@
         <v>45674</v>
       </c>
       <c r="K115" s="155"/>
-      <c r="L115" s="186" t="s">
+      <c r="L115" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="187"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="M115" s="184"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E116" s="154" t="s">
         <v>117</v>
       </c>
@@ -4493,7 +4532,7 @@
       <c r="L116" s="154"/>
       <c r="M116" s="155"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E117" s="154"/>
       <c r="F117" s="157"/>
       <c r="G117" s="157"/>
@@ -4501,10 +4540,10 @@
       <c r="I117" s="157"/>
       <c r="J117" s="157"/>
       <c r="K117" s="155"/>
-      <c r="L117" s="188"/>
-      <c r="M117" s="187"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L117" s="185"/>
+      <c r="M117" s="184"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E118" s="154" t="s">
         <v>48</v>
       </c>
@@ -4520,7 +4559,7 @@
       <c r="L118" s="154"/>
       <c r="M118" s="155"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E119" s="164" t="s">
         <v>118</v>
       </c>
@@ -4536,7 +4575,7 @@
       <c r="L119" s="154"/>
       <c r="M119" s="155"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E120" s="164" t="s">
         <v>122</v>
       </c>
@@ -4552,7 +4591,7 @@
       <c r="L120" s="154"/>
       <c r="M120" s="155"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E121" s="164"/>
       <c r="F121" s="157"/>
       <c r="G121" s="157"/>
@@ -4563,7 +4602,7 @@
       <c r="L121" s="154"/>
       <c r="M121" s="155"/>
     </row>
-    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E122" s="164"/>
       <c r="F122" s="157"/>
       <c r="G122" s="157"/>
@@ -4574,7 +4613,7 @@
       <c r="L122" s="154"/>
       <c r="M122" s="155"/>
     </row>
-    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F123" s="157"/>
       <c r="G123" s="157"/>
       <c r="H123" s="157"/>
@@ -4584,7 +4623,7 @@
       <c r="L123" s="154"/>
       <c r="M123" s="155"/>
     </row>
-    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E124" s="164"/>
       <c r="F124" s="157"/>
       <c r="G124" s="157"/>
@@ -4595,7 +4634,7 @@
       <c r="L124" s="154"/>
       <c r="M124" s="155"/>
     </row>
-    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E125" s="154"/>
       <c r="F125" s="157"/>
       <c r="G125" s="157"/>
@@ -4606,7 +4645,7 @@
       <c r="L125" s="154"/>
       <c r="M125" s="155"/>
     </row>
-    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E126" s="154"/>
       <c r="F126" s="157"/>
       <c r="G126" s="157"/>
@@ -4617,7 +4656,7 @@
       <c r="L126" s="154"/>
       <c r="M126" s="155"/>
     </row>
-    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E127" s="154"/>
       <c r="F127" s="157"/>
       <c r="G127" s="157"/>
@@ -4628,24 +4667,54 @@
       <c r="L127" s="165"/>
       <c r="M127" s="166"/>
     </row>
-    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="176" t="s">
+    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E128" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="177"/>
-      <c r="G128" s="177"/>
-      <c r="H128" s="177"/>
-      <c r="I128" s="177"/>
-      <c r="J128" s="178">
+      <c r="F128" s="193"/>
+      <c r="G128" s="193"/>
+      <c r="H128" s="193"/>
+      <c r="I128" s="193"/>
+      <c r="J128" s="194">
         <f>SUM(J118:J127)</f>
         <v>22771.405480000005</v>
       </c>
-      <c r="K128" s="179"/>
+      <c r="K128" s="195"/>
       <c r="L128" s="167"/>
       <c r="M128" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E108:K108"/>
+    <mergeCell ref="E109:K109"/>
+    <mergeCell ref="E113:K113"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="E56:K56"/>
+    <mergeCell ref="E57:K57"/>
+    <mergeCell ref="E61:K61"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="E76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L65:M65"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="A3:B4"/>
     <mergeCell ref="A5:B5"/>
@@ -4662,36 +4731,6 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="E76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E108:K108"/>
-    <mergeCell ref="E109:K109"/>
-    <mergeCell ref="E113:K113"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="E56:K56"/>
-    <mergeCell ref="E57:K57"/>
-    <mergeCell ref="E61:K61"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="E33:K33"/>
-    <mergeCell ref="E37:K37"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4700,18 +4739,2425 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8543EC9B-9161-45B2-8DCB-D5560AB9491C}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N129"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="218">
+        <v>552431</v>
+      </c>
+      <c r="E1" s="214">
+        <v>552431</v>
+      </c>
+      <c r="J1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="215" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="217">
+        <v>126714.2</v>
+      </c>
+      <c r="E2" s="216">
+        <v>126714.2</v>
+      </c>
+      <c r="H2" s="213"/>
+      <c r="I2" s="213"/>
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="97">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="B3" s="98"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="101"/>
+      <c r="K3" s="101"/>
+      <c r="L3" s="102"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="177" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="178"/>
+      <c r="C4" s="186" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="175" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="186" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="190" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="188" t="s">
+        <v>137</v>
+      </c>
+      <c r="K4" s="175" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="219" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="179"/>
+      <c r="B5" s="180"/>
+      <c r="C5" s="187"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="187"/>
+      <c r="H5" s="37">
+        <v>0.04</v>
+      </c>
+      <c r="I5" s="191"/>
+      <c r="J5" s="189"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="220"/>
+    </row>
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="181">
+        <v>1</v>
+      </c>
+      <c r="B6" s="182"/>
+      <c r="C6" s="110" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="58"/>
+      <c r="E6" s="149">
+        <v>0</v>
+      </c>
+      <c r="F6" s="150"/>
+      <c r="G6" s="151">
+        <f>E6-F6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="151">
+        <f>IF(G6&gt;0,G6*4%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="95">
+        <v>13.8</v>
+      </c>
+      <c r="J6" s="96">
+        <f>E$1*I6/100</f>
+        <v>76235.478000000003</v>
+      </c>
+      <c r="K6" s="142">
+        <f>E$2*I6/100</f>
+        <v>17486.559600000001</v>
+      </c>
+      <c r="L6" s="221">
+        <f>G6+H6+J6+K6</f>
+        <v>93722.037600000011</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
+        <v>2</v>
+      </c>
+      <c r="B7" s="182"/>
+      <c r="C7" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="149">
+        <v>0</v>
+      </c>
+      <c r="F7" s="150"/>
+      <c r="G7" s="151">
+        <f t="shared" ref="G7:G15" si="0">E7-F7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="151">
+        <f t="shared" ref="H7:H15" si="1">IF(G7&gt;0,G7*4%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="95">
+        <v>11.86</v>
+      </c>
+      <c r="J7" s="96">
+        <f t="shared" ref="J7:J15" si="2">E$1*I7/100</f>
+        <v>65518.316599999998</v>
+      </c>
+      <c r="K7" s="142">
+        <f t="shared" ref="K7:K15" si="3">E$2*I7/100</f>
+        <v>15028.304119999997</v>
+      </c>
+      <c r="L7" s="221">
+        <f t="shared" ref="L7:L15" si="4">G7+H7+J7+K7</f>
+        <v>80546.620719999992</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="181">
+        <v>3</v>
+      </c>
+      <c r="B8" s="182"/>
+      <c r="C8" s="110" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="72" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="149">
+        <v>0</v>
+      </c>
+      <c r="F8" s="150"/>
+      <c r="G8" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="95">
+        <v>12.46</v>
+      </c>
+      <c r="J8" s="96">
+        <f t="shared" si="2"/>
+        <v>68832.902600000001</v>
+      </c>
+      <c r="K8" s="142">
+        <f t="shared" si="3"/>
+        <v>15788.589320000001</v>
+      </c>
+      <c r="L8" s="221">
+        <f t="shared" si="4"/>
+        <v>84621.49192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="181">
+        <v>4</v>
+      </c>
+      <c r="B9" s="182"/>
+      <c r="C9" s="110" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="149">
+        <v>0</v>
+      </c>
+      <c r="F9" s="150"/>
+      <c r="G9" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="95">
+        <v>14.75</v>
+      </c>
+      <c r="J9" s="96">
+        <f t="shared" si="2"/>
+        <v>81483.572499999995</v>
+      </c>
+      <c r="K9" s="142">
+        <f t="shared" si="3"/>
+        <v>18690.344499999999</v>
+      </c>
+      <c r="L9" s="221">
+        <f t="shared" si="4"/>
+        <v>100173.91699999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="181">
+        <v>5</v>
+      </c>
+      <c r="B10" s="182"/>
+      <c r="C10" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="72" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="149">
+        <v>0</v>
+      </c>
+      <c r="F10" s="150"/>
+      <c r="G10" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="95">
+        <v>12.41</v>
+      </c>
+      <c r="J10" s="96">
+        <f t="shared" si="2"/>
+        <v>68556.687099999996</v>
+      </c>
+      <c r="K10" s="142">
+        <f t="shared" si="3"/>
+        <v>15725.23222</v>
+      </c>
+      <c r="L10" s="221">
+        <f>G10+H10+J10+K10</f>
+        <v>84281.919320000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="181">
+        <v>6</v>
+      </c>
+      <c r="B11" s="182"/>
+      <c r="C11" s="110" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="72"/>
+      <c r="E11" s="149">
+        <v>0</v>
+      </c>
+      <c r="F11" s="150"/>
+      <c r="G11" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="95">
+        <v>12.48</v>
+      </c>
+      <c r="J11" s="96">
+        <f t="shared" si="2"/>
+        <v>68943.388800000001</v>
+      </c>
+      <c r="K11" s="142">
+        <f t="shared" si="3"/>
+        <v>15813.93216</v>
+      </c>
+      <c r="L11" s="221">
+        <f t="shared" si="4"/>
+        <v>84757.320959999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="181">
+        <v>7</v>
+      </c>
+      <c r="B12" s="182"/>
+      <c r="C12" s="110" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="72"/>
+      <c r="E12" s="149">
+        <v>0</v>
+      </c>
+      <c r="F12" s="150"/>
+      <c r="G12" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="95">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="J12" s="96">
+        <f t="shared" si="2"/>
+        <v>100873.90060000001</v>
+      </c>
+      <c r="K12" s="142">
+        <f t="shared" si="3"/>
+        <v>23138.012920000005</v>
+      </c>
+      <c r="L12" s="221">
+        <f t="shared" si="4"/>
+        <v>124011.91352000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="181" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="182"/>
+      <c r="C13" s="110" t="str">
+        <f>C10</f>
+        <v>Grand Jorge</v>
+      </c>
+      <c r="D13" s="72"/>
+      <c r="E13" s="149">
+        <v>0</v>
+      </c>
+      <c r="F13" s="150"/>
+      <c r="G13" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="95">
+        <v>1.34</v>
+      </c>
+      <c r="J13" s="96">
+        <f t="shared" si="2"/>
+        <v>7402.5754000000006</v>
+      </c>
+      <c r="K13" s="142">
+        <f t="shared" si="3"/>
+        <v>1697.9702800000002</v>
+      </c>
+      <c r="L13" s="221">
+        <f t="shared" si="4"/>
+        <v>9100.5456800000011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="181" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="182"/>
+      <c r="C14" s="110" t="str">
+        <f>C7</f>
+        <v>Maceyle Gabriela</v>
+      </c>
+      <c r="D14" s="72"/>
+      <c r="E14" s="149">
+        <v>0</v>
+      </c>
+      <c r="F14" s="150"/>
+      <c r="G14" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="95">
+        <v>1.32</v>
+      </c>
+      <c r="J14" s="96">
+        <f t="shared" si="2"/>
+        <v>7292.0892000000003</v>
+      </c>
+      <c r="K14" s="142">
+        <f t="shared" si="3"/>
+        <v>1672.62744</v>
+      </c>
+      <c r="L14" s="221">
+        <f t="shared" si="4"/>
+        <v>8964.7166400000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="181" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="182"/>
+      <c r="C15" s="58" t="str">
+        <f>C7</f>
+        <v>Maceyle Gabriela</v>
+      </c>
+      <c r="D15" s="72"/>
+      <c r="E15" s="149">
+        <v>0</v>
+      </c>
+      <c r="F15" s="150"/>
+      <c r="G15" s="151">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="95">
+        <v>1.32</v>
+      </c>
+      <c r="J15" s="96">
+        <f t="shared" si="2"/>
+        <v>7292.0892000000003</v>
+      </c>
+      <c r="K15" s="142">
+        <f t="shared" si="3"/>
+        <v>1672.62744</v>
+      </c>
+      <c r="L15" s="221">
+        <f t="shared" si="4"/>
+        <v>8964.7166400000006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="104" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="105"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="106"/>
+      <c r="E16" s="42">
+        <f>SUM(E6:E15)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="107">
+        <f>SUM(F6:F15)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="107"/>
+      <c r="H16" s="108">
+        <f>SUM(H6:H15)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="109">
+        <f t="shared" ref="I16" si="5">SUM(I6:I15)</f>
+        <v>100</v>
+      </c>
+      <c r="J16" s="39">
+        <f>SUM(J6:J15)</f>
+        <v>552431.00000000012</v>
+      </c>
+      <c r="K16" s="42">
+        <f>SUM(K6:K12)</f>
+        <v>121670.97484000001</v>
+      </c>
+      <c r="L16" s="42">
+        <f>SUM(L6:L15)</f>
+        <v>679145.20000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19">
+        <v>7454</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="70"/>
+      <c r="E20">
+        <v>14805</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="31"/>
+    </row>
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21">
+        <v>3297</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="1"/>
+      <c r="E22">
+        <v>3177</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="37">
+        <v>0.02</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J22" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11">
+        <v>1</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="71"/>
+      <c r="E23">
+        <v>3056</v>
+      </c>
+      <c r="F23" s="46">
+        <v>37971</v>
+      </c>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50">
+        <v>0</v>
+      </c>
+      <c r="I23" s="17">
+        <v>0.121</v>
+      </c>
+      <c r="J23" s="44">
+        <f>0*I23</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="41"/>
+      <c r="L23" s="41" t="e">
+        <f>+#REF!+H23+J23</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>2</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="71"/>
+      <c r="E24">
+        <v>3056</v>
+      </c>
+      <c r="F24" s="46">
+        <v>66612</v>
+      </c>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50">
+        <v>0</v>
+      </c>
+      <c r="I24" s="17">
+        <v>0.122</v>
+      </c>
+      <c r="J24" s="44">
+        <f t="shared" ref="J24:J30" si="6">0*I24</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="41"/>
+      <c r="L24" s="41" t="e">
+        <f>+#REF!+H24+J24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11">
+        <v>3</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="71"/>
+      <c r="E25">
+        <f>SUM(E17:E24)</f>
+        <v>34845</v>
+      </c>
+      <c r="F25" s="46">
+        <v>0</v>
+      </c>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50">
+        <v>0</v>
+      </c>
+      <c r="I25" s="17">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="J25" s="44">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41" t="e">
+        <f>+#REF!+H25+J25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11">
+        <v>4</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="71"/>
+      <c r="F26" s="46">
+        <v>0</v>
+      </c>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50">
+        <v>0</v>
+      </c>
+      <c r="I26" s="17">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="J26" s="44">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41" t="e">
+        <f>+#REF!+H26+J26</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11">
+        <v>5</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="71"/>
+      <c r="F27" s="46">
+        <v>80517</v>
+      </c>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50">
+        <v>0</v>
+      </c>
+      <c r="I27" s="17">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="J27" s="44">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41" t="e">
+        <f>+#REF!+H27+J27</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11">
+        <v>6</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="71"/>
+      <c r="F28" s="46">
+        <v>0</v>
+      </c>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50">
+        <v>0</v>
+      </c>
+      <c r="I28" s="17">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="J28" s="44">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41" t="e">
+        <f>+#REF!+H28+J28</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11">
+        <v>7</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="71"/>
+      <c r="E29" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="46">
+        <v>18542</v>
+      </c>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50">
+        <v>0</v>
+      </c>
+      <c r="I29" s="17">
+        <v>0.127</v>
+      </c>
+      <c r="J29" s="44">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41" t="e">
+        <f>+#REF!+H29+J29</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11">
+        <v>8</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="71"/>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="46">
+        <v>0</v>
+      </c>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50">
+        <v>0</v>
+      </c>
+      <c r="I30" s="17">
+        <v>0.127</v>
+      </c>
+      <c r="J30" s="44">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41" t="e">
+        <f>+#REF!+H30+J30</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="69"/>
+      <c r="E31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="49">
+        <f>SUM(F23:F30)</f>
+        <v>203642</v>
+      </c>
+      <c r="G31" s="49"/>
+      <c r="H31" s="51">
+        <f>SUM(H23:H30)</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" ref="I31:J31" si="7">SUM(I23:I30)</f>
+        <v>1</v>
+      </c>
+      <c r="J31" s="39">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="42"/>
+      <c r="L31" s="42" t="e">
+        <f>SUM(L23:L30)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="N32"/>
+    </row>
+    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="196" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="197"/>
+      <c r="G33" s="197"/>
+      <c r="H33" s="197"/>
+      <c r="I33" s="197"/>
+      <c r="J33" s="197"/>
+      <c r="K33" s="195"/>
+      <c r="L33" s="152"/>
+      <c r="M33" s="153"/>
+      <c r="N33"/>
+    </row>
+    <row r="34" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="198" t="s">
+        <v>112</v>
+      </c>
+      <c r="F34" s="197"/>
+      <c r="G34" s="197"/>
+      <c r="H34" s="197"/>
+      <c r="I34" s="197"/>
+      <c r="J34" s="197"/>
+      <c r="K34" s="195"/>
+      <c r="L34" s="154"/>
+      <c r="M34" s="155"/>
+      <c r="N34"/>
+    </row>
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="156"/>
+      <c r="G35" s="156"/>
+      <c r="H35" s="156"/>
+      <c r="I35" s="157"/>
+      <c r="J35" s="157">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="155"/>
+      <c r="L35" s="154"/>
+      <c r="M35" s="155"/>
+      <c r="N35"/>
+    </row>
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="154" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" s="157"/>
+      <c r="G36" s="157"/>
+      <c r="H36" s="157"/>
+      <c r="I36" s="157"/>
+      <c r="J36" s="157"/>
+      <c r="K36" s="155"/>
+      <c r="L36" s="154"/>
+      <c r="M36" s="155"/>
+      <c r="N36"/>
+    </row>
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="158"/>
+      <c r="F37" s="159"/>
+      <c r="G37" s="159"/>
+      <c r="H37" s="159"/>
+      <c r="I37" s="159"/>
+      <c r="J37" s="159"/>
+      <c r="K37" s="160"/>
+      <c r="L37" s="154"/>
+      <c r="M37" s="155"/>
+      <c r="N37"/>
+    </row>
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="199" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" s="200"/>
+      <c r="G38" s="200"/>
+      <c r="H38" s="200"/>
+      <c r="I38" s="200"/>
+      <c r="J38" s="200"/>
+      <c r="K38" s="201"/>
+      <c r="L38" s="154"/>
+      <c r="M38" s="155"/>
+      <c r="N38"/>
+    </row>
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="154"/>
+      <c r="F39" s="157"/>
+      <c r="G39" s="157"/>
+      <c r="H39" s="157"/>
+      <c r="I39" s="157"/>
+      <c r="J39" s="157"/>
+      <c r="K39" s="155"/>
+      <c r="L39" s="154"/>
+      <c r="M39" s="155"/>
+      <c r="N39"/>
+    </row>
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="154" t="s">
+        <v>114</v>
+      </c>
+      <c r="F40" s="157"/>
+      <c r="G40" s="157" t="str">
+        <f>C8</f>
+        <v>Maceyle Gabriela</v>
+      </c>
+      <c r="H40" s="157"/>
+      <c r="I40" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J40" s="161">
+        <v>45674</v>
+      </c>
+      <c r="K40" s="155"/>
+      <c r="L40" s="183" t="s">
+        <v>116</v>
+      </c>
+      <c r="M40" s="184"/>
+      <c r="N40"/>
+    </row>
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="154" t="s">
+        <v>117</v>
+      </c>
+      <c r="F41" s="162">
+        <v>3</v>
+      </c>
+      <c r="G41" s="157"/>
+      <c r="H41" s="157"/>
+      <c r="I41" s="157"/>
+      <c r="J41" s="157"/>
+      <c r="K41" s="155"/>
+      <c r="L41" s="154"/>
+      <c r="M41" s="155"/>
+      <c r="N41"/>
+    </row>
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="154"/>
+      <c r="F42" s="157"/>
+      <c r="G42" s="157"/>
+      <c r="H42" s="157"/>
+      <c r="I42" s="157"/>
+      <c r="J42" s="157"/>
+      <c r="K42" s="155"/>
+      <c r="L42" s="185"/>
+      <c r="M42" s="184"/>
+      <c r="N42"/>
+    </row>
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" s="157"/>
+      <c r="G43" s="157"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="157"/>
+      <c r="J43" s="163">
+        <f>J8</f>
+        <v>68832.902600000001</v>
+      </c>
+      <c r="K43" s="155"/>
+      <c r="L43" s="154"/>
+      <c r="M43" s="155"/>
+      <c r="N43"/>
+    </row>
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="164" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="157"/>
+      <c r="G44" s="157"/>
+      <c r="H44" s="157"/>
+      <c r="I44" s="157"/>
+      <c r="J44" s="163">
+        <f>K8</f>
+        <v>15788.589320000001</v>
+      </c>
+      <c r="K44" s="155"/>
+      <c r="L44" s="154"/>
+      <c r="M44" s="155"/>
+      <c r="N44"/>
+    </row>
+    <row r="45" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="164" t="s">
+        <v>120</v>
+      </c>
+      <c r="F45" s="157"/>
+      <c r="G45" s="157"/>
+      <c r="H45" s="157"/>
+      <c r="I45" s="157"/>
+      <c r="J45" s="163">
+        <f>G8+H8</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="155"/>
+      <c r="L45" s="154"/>
+      <c r="M45" s="155"/>
+      <c r="N45"/>
+    </row>
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="164"/>
+      <c r="F46" s="157"/>
+      <c r="G46" s="157"/>
+      <c r="H46" s="157"/>
+      <c r="I46" s="157"/>
+      <c r="J46" s="163"/>
+      <c r="K46" s="155"/>
+      <c r="L46" s="154"/>
+      <c r="M46" s="155"/>
+      <c r="N46"/>
+    </row>
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="164"/>
+      <c r="F47" s="157"/>
+      <c r="G47" s="157"/>
+      <c r="H47" s="157"/>
+      <c r="I47" s="157"/>
+      <c r="J47" s="163"/>
+      <c r="K47" s="155"/>
+      <c r="L47" s="154"/>
+      <c r="M47" s="155"/>
+      <c r="N47"/>
+    </row>
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="F48" s="157"/>
+      <c r="G48" s="157"/>
+      <c r="H48" s="157"/>
+      <c r="I48" s="157"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="155"/>
+      <c r="L48" s="154"/>
+      <c r="M48" s="155"/>
+      <c r="N48"/>
+    </row>
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="164"/>
+      <c r="F49" s="157"/>
+      <c r="G49" s="157"/>
+      <c r="H49" s="157"/>
+      <c r="I49" s="157"/>
+      <c r="J49" s="163"/>
+      <c r="K49" s="155"/>
+      <c r="L49" s="154"/>
+      <c r="M49" s="155"/>
+      <c r="N49"/>
+    </row>
+    <row r="50" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="154"/>
+      <c r="F50" s="157"/>
+      <c r="G50" s="157"/>
+      <c r="H50" s="157"/>
+      <c r="I50" s="157"/>
+      <c r="J50" s="157"/>
+      <c r="K50" s="155"/>
+      <c r="L50" s="154"/>
+      <c r="M50" s="155"/>
+      <c r="N50"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="F51" s="157"/>
+      <c r="G51" s="157"/>
+      <c r="H51" s="157"/>
+      <c r="I51" s="157"/>
+      <c r="J51" s="157">
+        <f>77200-77124.2</f>
+        <v>75.80000000000291</v>
+      </c>
+      <c r="K51" s="155"/>
+      <c r="L51" s="154"/>
+      <c r="M51" s="155"/>
+      <c r="N51"/>
+    </row>
+    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="154"/>
+      <c r="F52" s="157"/>
+      <c r="G52" s="157"/>
+      <c r="H52" s="157"/>
+      <c r="I52" s="157"/>
+      <c r="J52" s="157"/>
+      <c r="K52" s="155"/>
+      <c r="L52" s="165"/>
+      <c r="M52" s="166"/>
+      <c r="N52"/>
+    </row>
+    <row r="53" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="F53" s="193"/>
+      <c r="G53" s="193"/>
+      <c r="H53" s="193"/>
+      <c r="I53" s="193"/>
+      <c r="J53" s="194">
+        <f>SUM(J43:J52)</f>
+        <v>84697.291920000003</v>
+      </c>
+      <c r="K53" s="195"/>
+      <c r="L53" s="167"/>
+      <c r="M53" s="168"/>
+      <c r="N53"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="N54"/>
+    </row>
+    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E57" s="196" t="s">
+        <v>111</v>
+      </c>
+      <c r="F57" s="197"/>
+      <c r="G57" s="197"/>
+      <c r="H57" s="197"/>
+      <c r="I57" s="197"/>
+      <c r="J57" s="197"/>
+      <c r="K57" s="195"/>
+      <c r="L57" s="152"/>
+      <c r="M57" s="153"/>
+    </row>
+    <row r="58" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E58" s="198" t="s">
+        <v>112</v>
+      </c>
+      <c r="F58" s="197"/>
+      <c r="G58" s="197"/>
+      <c r="H58" s="197"/>
+      <c r="I58" s="197"/>
+      <c r="J58" s="197"/>
+      <c r="K58" s="195"/>
+      <c r="L58" s="154"/>
+      <c r="M58" s="155"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E59" s="152"/>
+      <c r="F59" s="156"/>
+      <c r="G59" s="156"/>
+      <c r="H59" s="156"/>
+      <c r="I59" s="157"/>
+      <c r="J59" s="157">
+        <f>J35</f>
+        <v>0</v>
+      </c>
+      <c r="K59" s="155"/>
+      <c r="L59" s="154"/>
+      <c r="M59" s="155"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E60" s="154" t="s">
+        <v>113</v>
+      </c>
+      <c r="F60" s="157"/>
+      <c r="G60" s="157"/>
+      <c r="H60" s="157"/>
+      <c r="I60" s="157"/>
+      <c r="J60" s="157"/>
+      <c r="K60" s="155"/>
+      <c r="L60" s="154"/>
+      <c r="M60" s="155"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E61" s="158"/>
+      <c r="F61" s="159"/>
+      <c r="G61" s="159"/>
+      <c r="H61" s="159"/>
+      <c r="I61" s="159"/>
+      <c r="J61" s="159"/>
+      <c r="K61" s="160"/>
+      <c r="L61" s="154"/>
+      <c r="M61" s="155"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E62" s="199" t="s">
+        <v>49</v>
+      </c>
+      <c r="F62" s="200"/>
+      <c r="G62" s="200"/>
+      <c r="H62" s="200"/>
+      <c r="I62" s="200"/>
+      <c r="J62" s="200"/>
+      <c r="K62" s="201"/>
+      <c r="L62" s="154"/>
+      <c r="M62" s="155"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E63" s="154"/>
+      <c r="F63" s="157"/>
+      <c r="G63" s="157"/>
+      <c r="H63" s="157"/>
+      <c r="I63" s="157"/>
+      <c r="J63" s="157"/>
+      <c r="K63" s="155"/>
+      <c r="L63" s="154"/>
+      <c r="M63" s="155"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E64" s="154" t="s">
+        <v>114</v>
+      </c>
+      <c r="F64" s="157"/>
+      <c r="G64" s="162" t="str">
+        <f>C9</f>
+        <v>Castelao Lorena</v>
+      </c>
+      <c r="H64" s="157"/>
+      <c r="I64" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J64" s="161">
+        <v>45674</v>
+      </c>
+      <c r="K64" s="155"/>
+      <c r="L64" s="183" t="s">
+        <v>116</v>
+      </c>
+      <c r="M64" s="184"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E65" s="154" t="s">
+        <v>117</v>
+      </c>
+      <c r="F65" s="162">
+        <v>4</v>
+      </c>
+      <c r="G65" s="157"/>
+      <c r="H65" s="157"/>
+      <c r="I65" s="157"/>
+      <c r="J65" s="157"/>
+      <c r="K65" s="155"/>
+      <c r="L65" s="154"/>
+      <c r="M65" s="155"/>
+    </row>
+    <row r="66" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66" s="154"/>
+      <c r="F66" s="157"/>
+      <c r="G66" s="157"/>
+      <c r="H66" s="157"/>
+      <c r="I66" s="157"/>
+      <c r="J66" s="157"/>
+      <c r="K66" s="155"/>
+      <c r="L66" s="185"/>
+      <c r="M66" s="184"/>
+    </row>
+    <row r="67" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F67" s="157"/>
+      <c r="G67" s="157"/>
+      <c r="H67" s="157"/>
+      <c r="I67" s="157"/>
+      <c r="J67" s="163">
+        <f>J9</f>
+        <v>81483.572499999995</v>
+      </c>
+      <c r="K67" s="155"/>
+      <c r="L67" s="154"/>
+      <c r="M67" s="155"/>
+    </row>
+    <row r="68" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68" s="164" t="s">
+        <v>118</v>
+      </c>
+      <c r="F68" s="157"/>
+      <c r="G68" s="157"/>
+      <c r="H68" s="157"/>
+      <c r="I68" s="157"/>
+      <c r="J68" s="163">
+        <f>K9</f>
+        <v>18690.344499999999</v>
+      </c>
+      <c r="K68" s="155"/>
+      <c r="L68" s="154"/>
+      <c r="M68" s="155"/>
+    </row>
+    <row r="69" spans="1:13" s="21" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69" s="164" t="s">
+        <v>120</v>
+      </c>
+      <c r="F69" s="157"/>
+      <c r="G69" s="157"/>
+      <c r="H69" s="157"/>
+      <c r="I69" s="157"/>
+      <c r="J69" s="163">
+        <f>G30+H30</f>
+        <v>0</v>
+      </c>
+      <c r="K69" s="155"/>
+      <c r="L69" s="154"/>
+      <c r="M69" s="155"/>
+    </row>
+    <row r="70" spans="1:13" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70"/>
+      <c r="D70"/>
+      <c r="E70" s="164"/>
+      <c r="F70" s="157"/>
+      <c r="G70" s="157"/>
+      <c r="H70" s="157"/>
+      <c r="I70" s="157"/>
+      <c r="J70" s="163"/>
+      <c r="K70" s="155"/>
+      <c r="L70" s="154"/>
+      <c r="M70" s="155"/>
+    </row>
+    <row r="71" spans="1:13" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71" s="164"/>
+      <c r="F71" s="157"/>
+      <c r="G71" s="157"/>
+      <c r="H71" s="157"/>
+      <c r="I71" s="157"/>
+      <c r="J71" s="163"/>
+      <c r="K71" s="155"/>
+      <c r="L71" s="154"/>
+      <c r="M71" s="155"/>
+    </row>
+    <row r="72" spans="1:13" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72" s="157"/>
+      <c r="G72" s="157"/>
+      <c r="H72" s="157"/>
+      <c r="I72" s="157"/>
+      <c r="J72" s="163"/>
+      <c r="K72" s="155"/>
+      <c r="L72" s="154"/>
+      <c r="M72" s="155"/>
+    </row>
+    <row r="73" spans="1:13" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73"/>
+      <c r="D73"/>
+      <c r="E73" s="164"/>
+      <c r="F73" s="157"/>
+      <c r="G73" s="157"/>
+      <c r="H73" s="157"/>
+      <c r="I73" s="157"/>
+      <c r="J73" s="163"/>
+      <c r="K73" s="155"/>
+      <c r="L73" s="154"/>
+      <c r="M73" s="155"/>
+    </row>
+    <row r="74" spans="1:13" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74"/>
+      <c r="D74"/>
+      <c r="E74" s="154"/>
+      <c r="F74" s="157"/>
+      <c r="G74" s="157"/>
+      <c r="H74" s="157"/>
+      <c r="I74" s="157"/>
+      <c r="J74" s="157"/>
+      <c r="K74" s="155"/>
+      <c r="L74" s="154"/>
+      <c r="M74" s="155"/>
+    </row>
+    <row r="75" spans="1:13" s="21" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75"/>
+      <c r="D75"/>
+      <c r="E75" s="154"/>
+      <c r="F75" s="157"/>
+      <c r="G75" s="157"/>
+      <c r="H75" s="157"/>
+      <c r="I75" s="157"/>
+      <c r="J75" s="157"/>
+      <c r="K75" s="155"/>
+      <c r="L75" s="154"/>
+      <c r="M75" s="155"/>
+    </row>
+    <row r="76" spans="1:13" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76"/>
+      <c r="D76"/>
+      <c r="E76" s="154"/>
+      <c r="F76" s="157"/>
+      <c r="G76" s="157"/>
+      <c r="H76" s="157"/>
+      <c r="I76" s="157"/>
+      <c r="J76" s="157"/>
+      <c r="K76" s="155"/>
+      <c r="L76" s="165"/>
+      <c r="M76" s="166"/>
+    </row>
+    <row r="77" spans="1:13" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77"/>
+      <c r="D77"/>
+      <c r="E77" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="F77" s="193"/>
+      <c r="G77" s="193"/>
+      <c r="H77" s="193"/>
+      <c r="I77" s="193"/>
+      <c r="J77" s="194">
+        <f>SUM(J67:J76)</f>
+        <v>100173.91699999999</v>
+      </c>
+      <c r="K77" s="195"/>
+      <c r="L77" s="167"/>
+      <c r="M77" s="168"/>
+    </row>
+    <row r="83" spans="1:13" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83"/>
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
+      <c r="I83"/>
+      <c r="J83"/>
+      <c r="K83"/>
+      <c r="L83"/>
+      <c r="M83"/>
+    </row>
+    <row r="84" spans="1:13" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84" s="196" t="s">
+        <v>111</v>
+      </c>
+      <c r="F84" s="197"/>
+      <c r="G84" s="197"/>
+      <c r="H84" s="197"/>
+      <c r="I84" s="197"/>
+      <c r="J84" s="197"/>
+      <c r="K84" s="195"/>
+      <c r="L84" s="152"/>
+      <c r="M84" s="153"/>
+    </row>
+    <row r="85" spans="1:13" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85"/>
+      <c r="D85"/>
+      <c r="E85" s="198" t="s">
+        <v>112</v>
+      </c>
+      <c r="F85" s="197"/>
+      <c r="G85" s="197"/>
+      <c r="H85" s="197"/>
+      <c r="I85" s="197"/>
+      <c r="J85" s="197"/>
+      <c r="K85" s="195"/>
+      <c r="L85" s="154"/>
+      <c r="M85" s="155"/>
+    </row>
+    <row r="86" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86" s="152"/>
+      <c r="F86" s="156"/>
+      <c r="G86" s="156"/>
+      <c r="H86" s="156"/>
+      <c r="I86" s="157"/>
+      <c r="J86" s="157">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="K86" s="155"/>
+      <c r="L86" s="154"/>
+      <c r="M86" s="155"/>
+    </row>
+    <row r="87" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87" s="154" t="s">
+        <v>113</v>
+      </c>
+      <c r="F87" s="157"/>
+      <c r="G87" s="157"/>
+      <c r="H87" s="157"/>
+      <c r="I87" s="157"/>
+      <c r="J87" s="157"/>
+      <c r="K87" s="155"/>
+      <c r="L87" s="154"/>
+      <c r="M87" s="155"/>
+    </row>
+    <row r="88" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88"/>
+      <c r="D88"/>
+      <c r="E88" s="158"/>
+      <c r="F88" s="159"/>
+      <c r="G88" s="159"/>
+      <c r="H88" s="159"/>
+      <c r="I88" s="159"/>
+      <c r="J88" s="159"/>
+      <c r="K88" s="160"/>
+      <c r="L88" s="154"/>
+      <c r="M88" s="155"/>
+    </row>
+    <row r="89" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89" s="199" t="s">
+        <v>49</v>
+      </c>
+      <c r="F89" s="200"/>
+      <c r="G89" s="200"/>
+      <c r="H89" s="200"/>
+      <c r="I89" s="200"/>
+      <c r="J89" s="200"/>
+      <c r="K89" s="201"/>
+      <c r="L89" s="154"/>
+      <c r="M89" s="155"/>
+    </row>
+    <row r="90" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90" s="154"/>
+      <c r="F90" s="157"/>
+      <c r="G90" s="157"/>
+      <c r="H90" s="157"/>
+      <c r="I90" s="157"/>
+      <c r="J90" s="157"/>
+      <c r="K90" s="155"/>
+      <c r="L90" s="154"/>
+      <c r="M90" s="155"/>
+    </row>
+    <row r="91" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91" s="154" t="s">
+        <v>114</v>
+      </c>
+      <c r="F91" s="157"/>
+      <c r="G91" s="162" t="str">
+        <f>C11</f>
+        <v>Valdez Norberto</v>
+      </c>
+      <c r="H91" s="157"/>
+      <c r="I91" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J91" s="161">
+        <v>45674</v>
+      </c>
+      <c r="K91" s="155"/>
+      <c r="L91" s="183" t="s">
+        <v>116</v>
+      </c>
+      <c r="M91" s="184"/>
+    </row>
+    <row r="92" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92" s="154" t="s">
+        <v>117</v>
+      </c>
+      <c r="F92" s="162">
+        <v>6</v>
+      </c>
+      <c r="G92" s="157"/>
+      <c r="H92" s="157"/>
+      <c r="I92" s="157"/>
+      <c r="J92" s="157"/>
+      <c r="K92" s="155"/>
+      <c r="L92" s="154"/>
+      <c r="M92" s="155"/>
+    </row>
+    <row r="93" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93"/>
+      <c r="D93"/>
+      <c r="E93" s="154"/>
+      <c r="F93" s="157"/>
+      <c r="G93" s="157"/>
+      <c r="H93" s="157"/>
+      <c r="I93" s="157"/>
+      <c r="J93" s="157"/>
+      <c r="K93" s="155"/>
+      <c r="L93" s="185"/>
+      <c r="M93" s="184"/>
+    </row>
+    <row r="94" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F94" s="157"/>
+      <c r="G94" s="157"/>
+      <c r="H94" s="157"/>
+      <c r="I94" s="157"/>
+      <c r="J94" s="163">
+        <f>J11</f>
+        <v>68943.388800000001</v>
+      </c>
+      <c r="K94" s="155"/>
+      <c r="L94" s="154"/>
+      <c r="M94" s="155"/>
+    </row>
+    <row r="95" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95"/>
+      <c r="D95"/>
+      <c r="E95" s="164" t="s">
+        <v>118</v>
+      </c>
+      <c r="F95" s="157"/>
+      <c r="G95" s="157"/>
+      <c r="H95" s="157"/>
+      <c r="I95" s="157"/>
+      <c r="J95" s="163">
+        <f>K11</f>
+        <v>15813.93216</v>
+      </c>
+      <c r="K95" s="155"/>
+      <c r="L95" s="154"/>
+      <c r="M95" s="155"/>
+    </row>
+    <row r="96" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96"/>
+      <c r="D96"/>
+      <c r="E96" s="164" t="s">
+        <v>121</v>
+      </c>
+      <c r="F96" s="157"/>
+      <c r="G96" s="157"/>
+      <c r="H96" s="157"/>
+      <c r="I96" s="157"/>
+      <c r="J96" s="163">
+        <v>23.89</v>
+      </c>
+      <c r="K96" s="155"/>
+      <c r="L96" s="154"/>
+      <c r="M96" s="155"/>
+    </row>
+    <row r="97" spans="1:13" s="21" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97" s="164"/>
+      <c r="F97" s="157"/>
+      <c r="G97" s="157"/>
+      <c r="H97" s="157"/>
+      <c r="I97" s="157"/>
+      <c r="J97" s="163"/>
+      <c r="K97" s="155"/>
+      <c r="L97" s="154"/>
+      <c r="M97" s="155"/>
+    </row>
+    <row r="98" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="E98" s="164"/>
+      <c r="F98" s="157"/>
+      <c r="G98" s="157"/>
+      <c r="H98" s="157"/>
+      <c r="I98" s="157"/>
+      <c r="J98" s="163"/>
+      <c r="K98" s="155"/>
+      <c r="L98" s="154"/>
+      <c r="M98" s="155"/>
+    </row>
+    <row r="99" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99" s="157"/>
+      <c r="G99" s="157"/>
+      <c r="H99" s="157"/>
+      <c r="I99" s="157"/>
+      <c r="J99" s="163"/>
+      <c r="K99" s="155"/>
+      <c r="L99" s="154"/>
+      <c r="M99" s="155"/>
+    </row>
+    <row r="100" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100" s="164"/>
+      <c r="F100" s="157"/>
+      <c r="G100" s="157"/>
+      <c r="H100" s="157"/>
+      <c r="I100" s="157"/>
+      <c r="J100" s="163"/>
+      <c r="K100" s="155"/>
+      <c r="L100" s="154"/>
+      <c r="M100" s="155"/>
+    </row>
+    <row r="101" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101" s="154"/>
+      <c r="F101" s="157"/>
+      <c r="G101" s="157"/>
+      <c r="H101" s="157"/>
+      <c r="I101" s="157"/>
+      <c r="J101" s="157"/>
+      <c r="K101" s="155"/>
+      <c r="L101" s="154"/>
+      <c r="M101" s="155"/>
+    </row>
+    <row r="102" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102" s="154"/>
+      <c r="F102" s="157"/>
+      <c r="G102" s="157"/>
+      <c r="H102" s="157"/>
+      <c r="I102" s="157"/>
+      <c r="J102" s="157"/>
+      <c r="K102" s="155"/>
+      <c r="L102" s="154"/>
+      <c r="M102" s="155"/>
+    </row>
+    <row r="103" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103" s="154"/>
+      <c r="F103" s="157"/>
+      <c r="G103" s="157"/>
+      <c r="H103" s="157"/>
+      <c r="I103" s="157"/>
+      <c r="J103" s="157"/>
+      <c r="K103" s="155"/>
+      <c r="L103" s="165"/>
+      <c r="M103" s="166"/>
+    </row>
+    <row r="104" spans="1:13" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="F104" s="193"/>
+      <c r="G104" s="193"/>
+      <c r="H104" s="193"/>
+      <c r="I104" s="193"/>
+      <c r="J104" s="194">
+        <f>SUM(J94:J103)</f>
+        <v>84781.210959999997</v>
+      </c>
+      <c r="K104" s="195"/>
+      <c r="L104" s="167"/>
+      <c r="M104" s="168"/>
+    </row>
+    <row r="108" spans="1:13" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+      <c r="J108"/>
+      <c r="K108"/>
+      <c r="L108"/>
+      <c r="M108"/>
+    </row>
+    <row r="109" spans="1:13" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109" s="196" t="s">
+        <v>111</v>
+      </c>
+      <c r="F109" s="197"/>
+      <c r="G109" s="197"/>
+      <c r="H109" s="197"/>
+      <c r="I109" s="197"/>
+      <c r="J109" s="197"/>
+      <c r="K109" s="195"/>
+      <c r="L109" s="152"/>
+      <c r="M109" s="153"/>
+    </row>
+    <row r="110" spans="1:13" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110" s="198" t="s">
+        <v>112</v>
+      </c>
+      <c r="F110" s="197"/>
+      <c r="G110" s="197"/>
+      <c r="H110" s="197"/>
+      <c r="I110" s="197"/>
+      <c r="J110" s="197"/>
+      <c r="K110" s="195"/>
+      <c r="L110" s="154"/>
+      <c r="M110" s="155"/>
+    </row>
+    <row r="111" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111" s="152"/>
+      <c r="F111" s="156"/>
+      <c r="G111" s="156"/>
+      <c r="H111" s="156"/>
+      <c r="I111" s="157"/>
+      <c r="J111" s="157">
+        <f>'detalle y gastos'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="K111" s="155"/>
+      <c r="L111" s="154"/>
+      <c r="M111" s="155"/>
+    </row>
+    <row r="112" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112" s="154" t="s">
+        <v>113</v>
+      </c>
+      <c r="F112" s="157"/>
+      <c r="G112" s="157"/>
+      <c r="H112" s="157"/>
+      <c r="I112" s="157"/>
+      <c r="J112" s="157"/>
+      <c r="K112" s="155"/>
+      <c r="L112" s="154"/>
+      <c r="M112" s="155"/>
+    </row>
+    <row r="113" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113" s="158"/>
+      <c r="F113" s="159"/>
+      <c r="G113" s="159"/>
+      <c r="H113" s="159"/>
+      <c r="I113" s="159"/>
+      <c r="J113" s="159"/>
+      <c r="K113" s="160"/>
+      <c r="L113" s="154"/>
+      <c r="M113" s="155"/>
+    </row>
+    <row r="114" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114" s="199" t="s">
+        <v>49</v>
+      </c>
+      <c r="F114" s="200"/>
+      <c r="G114" s="200"/>
+      <c r="H114" s="200"/>
+      <c r="I114" s="200"/>
+      <c r="J114" s="200"/>
+      <c r="K114" s="201"/>
+      <c r="L114" s="154"/>
+      <c r="M114" s="155"/>
+    </row>
+    <row r="115" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115" s="154"/>
+      <c r="F115" s="157"/>
+      <c r="G115" s="157"/>
+      <c r="H115" s="157"/>
+      <c r="I115" s="157"/>
+      <c r="J115" s="157"/>
+      <c r="K115" s="155"/>
+      <c r="L115" s="154"/>
+      <c r="M115" s="155"/>
+    </row>
+    <row r="116" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116" s="154" t="s">
+        <v>114</v>
+      </c>
+      <c r="F116" s="157"/>
+      <c r="G116" s="162" t="str">
+        <f>C6</f>
+        <v>Gomez Elizabeth</v>
+      </c>
+      <c r="H116" s="157"/>
+      <c r="I116" s="157" t="s">
+        <v>115</v>
+      </c>
+      <c r="J116" s="161">
+        <v>45674</v>
+      </c>
+      <c r="K116" s="155"/>
+      <c r="L116" s="183" t="s">
+        <v>116</v>
+      </c>
+      <c r="M116" s="184"/>
+    </row>
+    <row r="117" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117" s="154" t="s">
+        <v>117</v>
+      </c>
+      <c r="F117" s="162">
+        <v>1</v>
+      </c>
+      <c r="G117" s="157"/>
+      <c r="H117" s="157"/>
+      <c r="I117" s="157"/>
+      <c r="J117" s="157"/>
+      <c r="K117" s="155"/>
+      <c r="L117" s="154"/>
+      <c r="M117" s="155"/>
+    </row>
+    <row r="118" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118" s="154"/>
+      <c r="F118" s="157"/>
+      <c r="G118" s="157"/>
+      <c r="H118" s="157"/>
+      <c r="I118" s="157"/>
+      <c r="J118" s="157"/>
+      <c r="K118" s="155"/>
+      <c r="L118" s="185"/>
+      <c r="M118" s="184"/>
+    </row>
+    <row r="119" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119" s="154" t="s">
+        <v>48</v>
+      </c>
+      <c r="F119" s="157"/>
+      <c r="G119" s="157"/>
+      <c r="H119" s="157"/>
+      <c r="I119" s="157"/>
+      <c r="J119" s="163">
+        <f>J6</f>
+        <v>76235.478000000003</v>
+      </c>
+      <c r="K119" s="155"/>
+      <c r="L119" s="154"/>
+      <c r="M119" s="155"/>
+    </row>
+    <row r="120" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120" s="164" t="s">
+        <v>118</v>
+      </c>
+      <c r="F120" s="157"/>
+      <c r="G120" s="157"/>
+      <c r="H120" s="157"/>
+      <c r="I120" s="157"/>
+      <c r="J120" s="163">
+        <f>K6</f>
+        <v>17486.559600000001</v>
+      </c>
+      <c r="K120" s="155"/>
+      <c r="L120" s="154"/>
+      <c r="M120" s="155"/>
+    </row>
+    <row r="121" spans="1:13" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121"/>
+      <c r="D121"/>
+      <c r="E121" s="164" t="s">
+        <v>122</v>
+      </c>
+      <c r="F121" s="157"/>
+      <c r="G121" s="157"/>
+      <c r="H121" s="157"/>
+      <c r="I121" s="157"/>
+      <c r="J121" s="163">
+        <f>-20862.34+20810</f>
+        <v>-52.340000000000146</v>
+      </c>
+      <c r="K121" s="155"/>
+      <c r="L121" s="154"/>
+      <c r="M121" s="155"/>
+    </row>
+    <row r="122" spans="1:13" s="21" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122" s="164"/>
+      <c r="F122" s="157"/>
+      <c r="G122" s="157"/>
+      <c r="H122" s="157"/>
+      <c r="I122" s="157"/>
+      <c r="J122" s="163"/>
+      <c r="K122" s="155"/>
+      <c r="L122" s="154"/>
+      <c r="M122" s="155"/>
+    </row>
+    <row r="123" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123" s="164"/>
+      <c r="F123" s="157"/>
+      <c r="G123" s="157"/>
+      <c r="H123" s="157"/>
+      <c r="I123" s="157"/>
+      <c r="J123" s="163"/>
+      <c r="K123" s="155"/>
+      <c r="L123" s="154"/>
+      <c r="M123" s="155"/>
+    </row>
+    <row r="124" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124"/>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124" s="157"/>
+      <c r="G124" s="157"/>
+      <c r="H124" s="157"/>
+      <c r="I124" s="157"/>
+      <c r="J124" s="163"/>
+      <c r="K124" s="155"/>
+      <c r="L124" s="154"/>
+      <c r="M124" s="155"/>
+    </row>
+    <row r="125" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125"/>
+      <c r="D125"/>
+      <c r="E125" s="164"/>
+      <c r="F125" s="157"/>
+      <c r="G125" s="157"/>
+      <c r="H125" s="157"/>
+      <c r="I125" s="157"/>
+      <c r="J125" s="163"/>
+      <c r="K125" s="155"/>
+      <c r="L125" s="154"/>
+      <c r="M125" s="155"/>
+    </row>
+    <row r="126" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126"/>
+      <c r="D126"/>
+      <c r="E126" s="154"/>
+      <c r="F126" s="157"/>
+      <c r="G126" s="157"/>
+      <c r="H126" s="157"/>
+      <c r="I126" s="157"/>
+      <c r="J126" s="157"/>
+      <c r="K126" s="155"/>
+      <c r="L126" s="154"/>
+      <c r="M126" s="155"/>
+    </row>
+    <row r="127" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127"/>
+      <c r="D127"/>
+      <c r="E127" s="154"/>
+      <c r="F127" s="157"/>
+      <c r="G127" s="157"/>
+      <c r="H127" s="157"/>
+      <c r="I127" s="157"/>
+      <c r="J127" s="157"/>
+      <c r="K127" s="155"/>
+      <c r="L127" s="154"/>
+      <c r="M127" s="155"/>
+    </row>
+    <row r="128" spans="1:13" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128"/>
+      <c r="D128"/>
+      <c r="E128" s="154"/>
+      <c r="F128" s="157"/>
+      <c r="G128" s="157"/>
+      <c r="H128" s="157"/>
+      <c r="I128" s="157"/>
+      <c r="J128" s="157"/>
+      <c r="K128" s="155"/>
+      <c r="L128" s="165"/>
+      <c r="M128" s="166"/>
+    </row>
+    <row r="129" spans="1:13" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="F129" s="193"/>
+      <c r="G129" s="193"/>
+      <c r="H129" s="193"/>
+      <c r="I129" s="193"/>
+      <c r="J129" s="194">
+        <f>SUM(J119:J128)</f>
+        <v>93669.697600000014</v>
+      </c>
+      <c r="K129" s="195"/>
+      <c r="L129" s="167"/>
+      <c r="M129" s="168"/>
+    </row>
+  </sheetData>
+  <mergeCells count="46">
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="E109:K109"/>
+    <mergeCell ref="E110:K110"/>
+    <mergeCell ref="E114:K114"/>
+    <mergeCell ref="L116:M116"/>
+    <mergeCell ref="L118:M118"/>
+    <mergeCell ref="E129:I129"/>
+    <mergeCell ref="J129:K129"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E85:K85"/>
+    <mergeCell ref="E89:K89"/>
+    <mergeCell ref="L91:M91"/>
+    <mergeCell ref="L93:M93"/>
+    <mergeCell ref="E104:I104"/>
+    <mergeCell ref="J104:K104"/>
+    <mergeCell ref="E57:K57"/>
+    <mergeCell ref="E58:K58"/>
+    <mergeCell ref="E62:K62"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="E77:I77"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="E34:K34"/>
+    <mergeCell ref="E38:K38"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="E53:I53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="I4:I5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="7" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" customWidth="1"/>
+    <col min="6" max="7" width="15.44140625" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="22.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B1" s="111" t="s">
         <v>79</v>
       </c>
@@ -4731,12 +7177,12 @@
       <c r="K1" s="114"/>
       <c r="L1" s="115"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="H2" s="116"/>
       <c r="I2" s="116"/>
       <c r="J2" s="116"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" s="117" t="s">
         <v>82</v>
       </c>
@@ -4763,7 +7209,7 @@
       <c r="K3" s="5"/>
       <c r="M3" s="119"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="117"/>
       <c r="C4" s="111" t="s">
         <v>88</v>
@@ -4780,7 +7226,7 @@
       <c r="I4" s="120"/>
       <c r="J4" s="120"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>90</v>
       </c>
@@ -4813,7 +7259,7 @@
       <c r="L5" s="122"/>
       <c r="M5" s="123"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>91</v>
       </c>
@@ -4846,7 +7292,7 @@
       <c r="L6" s="122"/>
       <c r="M6" s="123"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>92</v>
       </c>
@@ -4878,7 +7324,7 @@
       <c r="L7" s="122"/>
       <c r="M7" s="123"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>93</v>
       </c>
@@ -4911,7 +7357,7 @@
       <c r="L8" s="122"/>
       <c r="M8" s="123"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>94</v>
       </c>
@@ -4944,7 +7390,7 @@
       <c r="L9" s="122"/>
       <c r="M9" s="123"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>95</v>
       </c>
@@ -4977,7 +7423,7 @@
       <c r="L10" s="122"/>
       <c r="M10" s="123"/>
     </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>96</v>
       </c>
@@ -5010,7 +7456,7 @@
       <c r="L11" s="122"/>
       <c r="M11" s="123"/>
     </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="125"/>
       <c r="C12" s="126">
         <f>SUM(C5:C11)</f>
@@ -5038,13 +7484,13 @@
       <c r="K12" s="125"/>
       <c r="L12" s="128"/>
     </row>
-    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C13" s="129"/>
       <c r="H13" s="117"/>
       <c r="I13" s="117"/>
       <c r="J13" s="117"/>
     </row>
-    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>97</v>
       </c>
@@ -5056,7 +7502,7 @@
       <c r="I14" s="117"/>
       <c r="J14" s="117"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>98</v>
       </c>
@@ -5064,7 +7510,7 @@
       <c r="I15" s="117"/>
       <c r="J15" s="117"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="117"/>
       <c r="C16" s="111"/>
       <c r="D16" s="111"/>
@@ -5075,7 +7521,7 @@
       <c r="J16" s="111"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="117"/>
       <c r="C17" s="111"/>
       <c r="D17" s="111"/>
@@ -5085,12 +7531,12 @@
       <c r="I17" s="120"/>
       <c r="J17" s="120"/>
     </row>
-    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H18" s="117"/>
       <c r="I18" s="117"/>
       <c r="J18" s="117"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C19" s="131"/>
       <c r="D19" s="132"/>
       <c r="E19" s="132"/>
@@ -5103,7 +7549,7 @@
       <c r="L19" s="132"/>
       <c r="M19" s="134"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C20" s="135"/>
       <c r="E20" t="s">
         <v>99</v>
@@ -5119,7 +7565,7 @@
       </c>
       <c r="M20" s="137"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C21" s="135"/>
       <c r="D21" t="s">
         <v>101</v>
@@ -5141,7 +7587,7 @@
       </c>
       <c r="M21" s="137"/>
     </row>
-    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C22" s="138"/>
       <c r="D22" s="139"/>
       <c r="E22" s="139"/>
@@ -5154,16 +7600,16 @@
       <c r="L22" s="139"/>
       <c r="M22" s="140"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="K25" s="141" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G26" s="5"/>
       <c r="K26" s="119"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="I27" t="s">
         <v>105</v>
       </c>
@@ -5174,7 +7620,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
         <v>95</v>
@@ -5190,7 +7636,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J31" t="s">
         <v>107</v>
       </c>
@@ -5198,7 +7644,7 @@
         <v>117067</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="J32" t="s">
         <v>108</v>
       </c>
@@ -5206,7 +7652,7 @@
         <v>-55000</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J33" s="119" t="s">
         <v>109</v>
       </c>
@@ -5214,7 +7660,7 @@
         <v>43965</v>
       </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K34" s="113">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
@@ -5226,25 +7672,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="0.140625" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="0.109375" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D1" s="55">
         <v>50000</v>
       </c>
@@ -5254,14 +7700,14 @@
       <c r="I1" s="207"/>
       <c r="J1" s="207"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="52" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>56</v>
       </c>
@@ -5284,7 +7730,7 @@
       <c r="N3" s="31"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -5327,7 +7773,7 @@
       </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -5358,7 +7804,7 @@
       <c r="N5" s="204"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -5406,7 +7852,7 @@
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>2</v>
       </c>
@@ -5454,7 +7900,7 @@
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>3</v>
       </c>
@@ -5502,7 +7948,7 @@
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>4</v>
       </c>
@@ -5550,7 +7996,7 @@
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>5</v>
       </c>
@@ -5598,7 +8044,7 @@
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>6</v>
       </c>
@@ -5646,7 +8092,7 @@
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>7</v>
       </c>
@@ -5694,7 +8140,7 @@
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>8</v>
       </c>
@@ -5742,7 +8188,7 @@
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -5802,48 +8248,48 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{434C3368-DE46-4844-AE9C-0C1B6FC5250E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="1.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5703125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="1.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="209" t="s">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="211" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="209" t="s">
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="211" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="209"/>
-      <c r="H1" s="209"/>
-      <c r="I1" s="210">
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="212">
         <v>800000</v>
       </c>
-      <c r="J1" s="210"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J1" s="212"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="97"/>
       <c r="B2" s="98"/>
       <c r="C2" s="99"/>
@@ -5857,15 +8303,15 @@
       <c r="K2" s="101"/>
       <c r="L2" s="102"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="199" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="177" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="200"/>
-      <c r="C3" s="189" t="s">
+      <c r="B3" s="178"/>
+      <c r="C3" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="197" t="s">
+      <c r="D3" s="175" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -5874,50 +8320,50 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="189" t="s">
+      <c r="G3" s="186" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="189" t="s">
+      <c r="H3" s="186" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="195" t="s">
+      <c r="I3" s="190" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="197" t="s">
+      <c r="J3" s="175" t="s">
         <v>128</v>
       </c>
       <c r="K3" s="170" t="s">
         <v>127</v>
       </c>
-      <c r="L3" s="211" t="s">
+      <c r="L3" s="208" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="201"/>
-      <c r="B4" s="202"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="198"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="179"/>
+      <c r="B4" s="180"/>
+      <c r="C4" s="187"/>
+      <c r="D4" s="176"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="196"/>
-      <c r="J4" s="198"/>
+      <c r="G4" s="187"/>
+      <c r="H4" s="187"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="176"/>
       <c r="K4" s="171" t="s">
         <v>129</v>
       </c>
-      <c r="L4" s="212"/>
-    </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="193">
+      <c r="L4" s="209"/>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="181">
         <v>1</v>
       </c>
-      <c r="B5" s="194"/>
+      <c r="B5" s="182"/>
       <c r="C5" s="110" t="s">
         <v>65</v>
       </c>
@@ -5953,11 +8399,11 @@
         <v>110400</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="193">
+    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A6" s="181">
         <v>2</v>
       </c>
-      <c r="B6" s="194"/>
+      <c r="B6" s="182"/>
       <c r="C6" s="110" t="s">
         <v>66</v>
       </c>
@@ -5995,11 +8441,11 @@
         <v>64880.003495999961</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="193">
+    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
+      <c r="A7" s="181">
         <v>3</v>
       </c>
-      <c r="B7" s="194"/>
+      <c r="B7" s="182"/>
       <c r="C7" s="110" t="s">
         <v>66</v>
       </c>
@@ -6037,11 +8483,11 @@
         <v>99680</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="193">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="181">
         <v>4</v>
       </c>
-      <c r="B8" s="194"/>
+      <c r="B8" s="182"/>
       <c r="C8" s="110" t="s">
         <v>67</v>
       </c>
@@ -6079,11 +8525,11 @@
         <v>118000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="193">
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="181">
         <v>5</v>
       </c>
-      <c r="B9" s="194"/>
+      <c r="B9" s="182"/>
       <c r="C9" s="110" t="s">
         <v>68</v>
       </c>
@@ -6121,11 +8567,11 @@
         <v>99279.992624999984</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="193">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="181">
         <v>6</v>
       </c>
-      <c r="B10" s="194"/>
+      <c r="B10" s="182"/>
       <c r="C10" s="110" t="s">
         <v>69</v>
       </c>
@@ -6161,11 +8607,11 @@
         <v>94999.311648000003</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="193">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="181">
         <v>7</v>
       </c>
-      <c r="B11" s="194"/>
+      <c r="B11" s="182"/>
       <c r="C11" s="110" t="s">
         <v>70</v>
       </c>
@@ -6201,11 +8647,11 @@
         <v>146080.00000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="193" t="s">
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="181" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="194"/>
+      <c r="B12" s="182"/>
       <c r="C12" s="110" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -6242,11 +8688,11 @@
         <v>10720</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="193" t="s">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="181" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="194"/>
+      <c r="B13" s="182"/>
       <c r="C13" s="110" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6283,11 +8729,11 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="193" t="s">
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="181" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="194"/>
+      <c r="B14" s="182"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6324,7 +8770,7 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="104" t="s">
         <v>11</v>
       </c>
@@ -6364,7 +8810,7 @@
         <v>765159.30776899995</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="52" t="s">
         <v>49</v>
       </c>
@@ -6372,7 +8818,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>51</v>
       </c>
@@ -6390,7 +8836,7 @@
       <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -6422,7 +8868,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6448,7 +8894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -6482,7 +8928,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -6516,7 +8962,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -6551,7 +8997,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -6582,7 +9028,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -6613,7 +9059,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -6644,7 +9090,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -6678,7 +9124,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -6712,7 +9158,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -6745,44 +9191,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="180" t="s">
+      <c r="E32" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="181"/>
-      <c r="I32" s="181"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="179"/>
+      <c r="F32" s="197"/>
+      <c r="G32" s="197"/>
+      <c r="H32" s="197"/>
+      <c r="I32" s="197"/>
+      <c r="J32" s="197"/>
+      <c r="K32" s="195"/>
       <c r="L32" s="152"/>
       <c r="M32" s="153"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="182" t="s">
+      <c r="E33" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="181"/>
-      <c r="G33" s="181"/>
-      <c r="H33" s="181"/>
-      <c r="I33" s="181"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="179"/>
+      <c r="F33" s="197"/>
+      <c r="G33" s="197"/>
+      <c r="H33" s="197"/>
+      <c r="I33" s="197"/>
+      <c r="J33" s="197"/>
+      <c r="K33" s="195"/>
       <c r="L33" s="154"/>
       <c r="M33" s="155"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="152"/>
@@ -6799,7 +9245,7 @@
       <c r="M34" s="155"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="154" t="s">
@@ -6815,7 +9261,7 @@
       <c r="M35" s="155"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="158"/>
@@ -6829,23 +9275,23 @@
       <c r="M36" s="155"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="183" t="s">
+      <c r="E37" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="185"/>
+      <c r="F37" s="200"/>
+      <c r="G37" s="200"/>
+      <c r="H37" s="200"/>
+      <c r="I37" s="200"/>
+      <c r="J37" s="200"/>
+      <c r="K37" s="201"/>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="154"/>
@@ -6859,7 +9305,7 @@
       <c r="M38" s="155"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="154" t="s">
@@ -6878,13 +9324,13 @@
         <v>45674</v>
       </c>
       <c r="K39" s="155"/>
-      <c r="L39" s="186" t="s">
+      <c r="L39" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="187"/>
+      <c r="M39" s="184"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="154" t="s">
@@ -6902,7 +9348,7 @@
       <c r="M40" s="155"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="154"/>
@@ -6912,11 +9358,11 @@
       <c r="I41" s="157"/>
       <c r="J41" s="157"/>
       <c r="K41" s="155"/>
-      <c r="L41" s="188"/>
-      <c r="M41" s="187"/>
+      <c r="L41" s="185"/>
+      <c r="M41" s="184"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="154" t="s">
@@ -6935,7 +9381,7 @@
       <c r="M42" s="155"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="164" t="s">
@@ -6954,7 +9400,7 @@
       <c r="M43" s="155"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="164" t="s">
@@ -6973,7 +9419,7 @@
       <c r="M44" s="155"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="164"/>
@@ -6987,7 +9433,7 @@
       <c r="M45" s="155"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="164"/>
@@ -7001,7 +9447,7 @@
       <c r="M46" s="155"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="157"/>
@@ -7014,7 +9460,7 @@
       <c r="M47" s="155"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="164"/>
@@ -7028,7 +9474,7 @@
       <c r="M48" s="155"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="154"/>
@@ -7042,7 +9488,7 @@
       <c r="M49" s="155"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="154" t="s">
@@ -7061,7 +9507,7 @@
       <c r="M50" s="155"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="154"/>
@@ -7075,58 +9521,58 @@
       <c r="M51" s="166"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="176" t="s">
+      <c r="E52" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="177"/>
-      <c r="G52" s="177"/>
-      <c r="H52" s="177"/>
-      <c r="I52" s="177"/>
-      <c r="J52" s="178">
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="194">
         <f>SUM(J42:J51)</f>
         <v>99755.8</v>
       </c>
-      <c r="K52" s="179"/>
+      <c r="K52" s="195"/>
       <c r="L52" s="167"/>
       <c r="M52" s="168"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="180" t="s">
+    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E56" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="181"/>
-      <c r="G56" s="181"/>
-      <c r="H56" s="181"/>
-      <c r="I56" s="181"/>
-      <c r="J56" s="181"/>
-      <c r="K56" s="179"/>
+      <c r="F56" s="197"/>
+      <c r="G56" s="197"/>
+      <c r="H56" s="197"/>
+      <c r="I56" s="197"/>
+      <c r="J56" s="197"/>
+      <c r="K56" s="195"/>
       <c r="L56" s="152"/>
       <c r="M56" s="153"/>
     </row>
-    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="182" t="s">
+    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E57" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="181"/>
-      <c r="G57" s="181"/>
-      <c r="H57" s="181"/>
-      <c r="I57" s="181"/>
-      <c r="J57" s="181"/>
-      <c r="K57" s="179"/>
+      <c r="F57" s="197"/>
+      <c r="G57" s="197"/>
+      <c r="H57" s="197"/>
+      <c r="I57" s="197"/>
+      <c r="J57" s="197"/>
+      <c r="K57" s="195"/>
       <c r="L57" s="154"/>
       <c r="M57" s="155"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E58" s="152"/>
       <c r="F58" s="156"/>
       <c r="G58" s="156"/>
@@ -7140,7 +9586,7 @@
       <c r="L58" s="154"/>
       <c r="M58" s="155"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E59" s="154" t="s">
         <v>113</v>
       </c>
@@ -7153,7 +9599,7 @@
       <c r="L59" s="154"/>
       <c r="M59" s="155"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E60" s="158"/>
       <c r="F60" s="159"/>
       <c r="G60" s="159"/>
@@ -7164,20 +9610,20 @@
       <c r="L60" s="154"/>
       <c r="M60" s="155"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="183" t="s">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="E61" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="184"/>
-      <c r="G61" s="184"/>
-      <c r="H61" s="184"/>
-      <c r="I61" s="184"/>
-      <c r="J61" s="184"/>
-      <c r="K61" s="185"/>
+      <c r="F61" s="200"/>
+      <c r="G61" s="200"/>
+      <c r="H61" s="200"/>
+      <c r="I61" s="200"/>
+      <c r="J61" s="200"/>
+      <c r="K61" s="201"/>
       <c r="L61" s="154"/>
       <c r="M61" s="155"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E62" s="154"/>
       <c r="F62" s="157"/>
       <c r="G62" s="157"/>
@@ -7188,7 +9634,7 @@
       <c r="L62" s="154"/>
       <c r="M62" s="155"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E63" s="154" t="s">
         <v>114</v>
       </c>
@@ -7205,12 +9651,12 @@
         <v>45674</v>
       </c>
       <c r="K63" s="155"/>
-      <c r="L63" s="186" t="s">
+      <c r="L63" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="187"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="M63" s="184"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
       <c r="E64" s="154" t="s">
         <v>117</v>
       </c>
@@ -7225,7 +9671,7 @@
       <c r="L64" s="154"/>
       <c r="M64" s="155"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E65" s="154"/>
       <c r="F65" s="157"/>
       <c r="G65" s="157"/>
@@ -7233,10 +9679,10 @@
       <c r="I65" s="157"/>
       <c r="J65" s="157"/>
       <c r="K65" s="155"/>
-      <c r="L65" s="188"/>
-      <c r="M65" s="187"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L65" s="185"/>
+      <c r="M65" s="184"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E66" s="154" t="s">
         <v>48</v>
       </c>
@@ -7252,7 +9698,7 @@
       <c r="L66" s="154"/>
       <c r="M66" s="155"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E67" s="164" t="s">
         <v>118</v>
       </c>
@@ -7268,7 +9714,7 @@
       <c r="L67" s="154"/>
       <c r="M67" s="155"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E68" s="164" t="s">
         <v>120</v>
       </c>
@@ -7284,7 +9730,7 @@
       <c r="L68" s="154"/>
       <c r="M68" s="155"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E69" s="164"/>
       <c r="F69" s="157"/>
       <c r="G69" s="157"/>
@@ -7295,7 +9741,7 @@
       <c r="L69" s="154"/>
       <c r="M69" s="155"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E70" s="164"/>
       <c r="F70" s="157"/>
       <c r="G70" s="157"/>
@@ -7306,7 +9752,7 @@
       <c r="L70" s="154"/>
       <c r="M70" s="155"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="F71" s="157"/>
       <c r="G71" s="157"/>
       <c r="H71" s="157"/>
@@ -7316,7 +9762,7 @@
       <c r="L71" s="154"/>
       <c r="M71" s="155"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E72" s="164"/>
       <c r="F72" s="157"/>
       <c r="G72" s="157"/>
@@ -7327,7 +9773,7 @@
       <c r="L72" s="154"/>
       <c r="M72" s="155"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E73" s="154"/>
       <c r="F73" s="157"/>
       <c r="G73" s="157"/>
@@ -7338,7 +9784,7 @@
       <c r="L73" s="154"/>
       <c r="M73" s="155"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="E74" s="154"/>
       <c r="F74" s="157"/>
       <c r="G74" s="157"/>
@@ -7349,7 +9795,7 @@
       <c r="L74" s="154"/>
       <c r="M74" s="155"/>
     </row>
-    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E75" s="154"/>
       <c r="F75" s="157"/>
       <c r="G75" s="157"/>
@@ -7360,50 +9806,50 @@
       <c r="L75" s="165"/>
       <c r="M75" s="166"/>
     </row>
-    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="176" t="s">
+    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E76" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="177"/>
-      <c r="G76" s="177"/>
-      <c r="H76" s="177"/>
-      <c r="I76" s="177"/>
-      <c r="J76" s="178">
+      <c r="F76" s="193"/>
+      <c r="G76" s="193"/>
+      <c r="H76" s="193"/>
+      <c r="I76" s="193"/>
+      <c r="J76" s="194">
         <f>SUM(J66:J75)</f>
         <v>118000</v>
       </c>
-      <c r="K76" s="179"/>
+      <c r="K76" s="195"/>
       <c r="L76" s="167"/>
       <c r="M76" s="168"/>
     </row>
-    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="180" t="s">
+    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E83" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="181"/>
-      <c r="G83" s="181"/>
-      <c r="H83" s="181"/>
-      <c r="I83" s="181"/>
-      <c r="J83" s="181"/>
-      <c r="K83" s="179"/>
+      <c r="F83" s="197"/>
+      <c r="G83" s="197"/>
+      <c r="H83" s="197"/>
+      <c r="I83" s="197"/>
+      <c r="J83" s="197"/>
+      <c r="K83" s="195"/>
       <c r="L83" s="152"/>
       <c r="M83" s="153"/>
     </row>
-    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="182" t="s">
+    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E84" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="181"/>
-      <c r="G84" s="181"/>
-      <c r="H84" s="181"/>
-      <c r="I84" s="181"/>
-      <c r="J84" s="181"/>
-      <c r="K84" s="179"/>
+      <c r="F84" s="197"/>
+      <c r="G84" s="197"/>
+      <c r="H84" s="197"/>
+      <c r="I84" s="197"/>
+      <c r="J84" s="197"/>
+      <c r="K84" s="195"/>
       <c r="L84" s="154"/>
       <c r="M84" s="155"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E85" s="152"/>
       <c r="F85" s="156"/>
       <c r="G85" s="156"/>
@@ -7417,7 +9863,7 @@
       <c r="L85" s="154"/>
       <c r="M85" s="155"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E86" s="154" t="s">
         <v>113</v>
       </c>
@@ -7430,7 +9876,7 @@
       <c r="L86" s="154"/>
       <c r="M86" s="155"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E87" s="158"/>
       <c r="F87" s="159"/>
       <c r="G87" s="159"/>
@@ -7441,20 +9887,20 @@
       <c r="L87" s="154"/>
       <c r="M87" s="155"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="183" t="s">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E88" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="184"/>
-      <c r="G88" s="184"/>
-      <c r="H88" s="184"/>
-      <c r="I88" s="184"/>
-      <c r="J88" s="184"/>
-      <c r="K88" s="185"/>
+      <c r="F88" s="200"/>
+      <c r="G88" s="200"/>
+      <c r="H88" s="200"/>
+      <c r="I88" s="200"/>
+      <c r="J88" s="200"/>
+      <c r="K88" s="201"/>
       <c r="L88" s="154"/>
       <c r="M88" s="155"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E89" s="154"/>
       <c r="F89" s="157"/>
       <c r="G89" s="157"/>
@@ -7465,7 +9911,7 @@
       <c r="L89" s="154"/>
       <c r="M89" s="155"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E90" s="154" t="s">
         <v>114</v>
       </c>
@@ -7482,12 +9928,12 @@
         <v>45674</v>
       </c>
       <c r="K90" s="155"/>
-      <c r="L90" s="186" t="s">
+      <c r="L90" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="187"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="M90" s="184"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E91" s="154" t="s">
         <v>117</v>
       </c>
@@ -7502,7 +9948,7 @@
       <c r="L91" s="154"/>
       <c r="M91" s="155"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E92" s="154"/>
       <c r="F92" s="157"/>
       <c r="G92" s="157"/>
@@ -7510,10 +9956,10 @@
       <c r="I92" s="157"/>
       <c r="J92" s="157"/>
       <c r="K92" s="155"/>
-      <c r="L92" s="188"/>
-      <c r="M92" s="187"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L92" s="185"/>
+      <c r="M92" s="184"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E93" s="154" t="s">
         <v>48</v>
       </c>
@@ -7529,7 +9975,7 @@
       <c r="L93" s="154"/>
       <c r="M93" s="155"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E94" s="164" t="s">
         <v>118</v>
       </c>
@@ -7545,7 +9991,7 @@
       <c r="L94" s="154"/>
       <c r="M94" s="155"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E95" s="164" t="s">
         <v>121</v>
       </c>
@@ -7560,7 +10006,7 @@
       <c r="L95" s="154"/>
       <c r="M95" s="155"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E96" s="164"/>
       <c r="F96" s="157"/>
       <c r="G96" s="157"/>
@@ -7571,7 +10017,7 @@
       <c r="L96" s="154"/>
       <c r="M96" s="155"/>
     </row>
-    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E97" s="164"/>
       <c r="F97" s="157"/>
       <c r="G97" s="157"/>
@@ -7582,7 +10028,7 @@
       <c r="L97" s="154"/>
       <c r="M97" s="155"/>
     </row>
-    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F98" s="157"/>
       <c r="G98" s="157"/>
       <c r="H98" s="157"/>
@@ -7592,7 +10038,7 @@
       <c r="L98" s="154"/>
       <c r="M98" s="155"/>
     </row>
-    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E99" s="164"/>
       <c r="F99" s="157"/>
       <c r="G99" s="157"/>
@@ -7603,7 +10049,7 @@
       <c r="L99" s="154"/>
       <c r="M99" s="155"/>
     </row>
-    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E100" s="154"/>
       <c r="F100" s="157"/>
       <c r="G100" s="157"/>
@@ -7614,7 +10060,7 @@
       <c r="L100" s="154"/>
       <c r="M100" s="155"/>
     </row>
-    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E101" s="154"/>
       <c r="F101" s="157"/>
       <c r="G101" s="157"/>
@@ -7625,7 +10071,7 @@
       <c r="L101" s="154"/>
       <c r="M101" s="155"/>
     </row>
-    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E102" s="154"/>
       <c r="F102" s="157"/>
       <c r="G102" s="157"/>
@@ -7636,50 +10082,50 @@
       <c r="L102" s="165"/>
       <c r="M102" s="166"/>
     </row>
-    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="176" t="s">
+    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E103" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="177"/>
-      <c r="G103" s="177"/>
-      <c r="H103" s="177"/>
-      <c r="I103" s="177"/>
-      <c r="J103" s="178">
+      <c r="F103" s="193"/>
+      <c r="G103" s="193"/>
+      <c r="H103" s="193"/>
+      <c r="I103" s="193"/>
+      <c r="J103" s="194">
         <f>SUM(J93:J102)</f>
         <v>99863.89</v>
       </c>
-      <c r="K103" s="179"/>
+      <c r="K103" s="195"/>
       <c r="L103" s="167"/>
       <c r="M103" s="168"/>
     </row>
-    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="180" t="s">
+    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E108" s="196" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="181"/>
-      <c r="G108" s="181"/>
-      <c r="H108" s="181"/>
-      <c r="I108" s="181"/>
-      <c r="J108" s="181"/>
-      <c r="K108" s="179"/>
+      <c r="F108" s="197"/>
+      <c r="G108" s="197"/>
+      <c r="H108" s="197"/>
+      <c r="I108" s="197"/>
+      <c r="J108" s="197"/>
+      <c r="K108" s="195"/>
       <c r="L108" s="152"/>
       <c r="M108" s="153"/>
     </row>
-    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="182" t="s">
+    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E109" s="198" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="181"/>
-      <c r="G109" s="181"/>
-      <c r="H109" s="181"/>
-      <c r="I109" s="181"/>
-      <c r="J109" s="181"/>
-      <c r="K109" s="179"/>
+      <c r="F109" s="197"/>
+      <c r="G109" s="197"/>
+      <c r="H109" s="197"/>
+      <c r="I109" s="197"/>
+      <c r="J109" s="197"/>
+      <c r="K109" s="195"/>
       <c r="L109" s="154"/>
       <c r="M109" s="155"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E110" s="152"/>
       <c r="F110" s="156"/>
       <c r="G110" s="156"/>
@@ -7693,7 +10139,7 @@
       <c r="L110" s="154"/>
       <c r="M110" s="155"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E111" s="154" t="s">
         <v>113</v>
       </c>
@@ -7706,7 +10152,7 @@
       <c r="L111" s="154"/>
       <c r="M111" s="155"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E112" s="158"/>
       <c r="F112" s="159"/>
       <c r="G112" s="159"/>
@@ -7717,20 +10163,20 @@
       <c r="L112" s="154"/>
       <c r="M112" s="155"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="183" t="s">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="E113" s="199" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="184"/>
-      <c r="G113" s="184"/>
-      <c r="H113" s="184"/>
-      <c r="I113" s="184"/>
-      <c r="J113" s="184"/>
-      <c r="K113" s="185"/>
+      <c r="F113" s="200"/>
+      <c r="G113" s="200"/>
+      <c r="H113" s="200"/>
+      <c r="I113" s="200"/>
+      <c r="J113" s="200"/>
+      <c r="K113" s="201"/>
       <c r="L113" s="154"/>
       <c r="M113" s="155"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E114" s="154"/>
       <c r="F114" s="157"/>
       <c r="G114" s="157"/>
@@ -7741,7 +10187,7 @@
       <c r="L114" s="154"/>
       <c r="M114" s="155"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E115" s="154" t="s">
         <v>114</v>
       </c>
@@ -7758,12 +10204,12 @@
         <v>45674</v>
       </c>
       <c r="K115" s="155"/>
-      <c r="L115" s="186" t="s">
+      <c r="L115" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="187"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="M115" s="184"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E116" s="154" t="s">
         <v>117</v>
       </c>
@@ -7778,7 +10224,7 @@
       <c r="L116" s="154"/>
       <c r="M116" s="155"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E117" s="154"/>
       <c r="F117" s="157"/>
       <c r="G117" s="157"/>
@@ -7786,10 +10232,10 @@
       <c r="I117" s="157"/>
       <c r="J117" s="157"/>
       <c r="K117" s="155"/>
-      <c r="L117" s="188"/>
-      <c r="M117" s="187"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L117" s="185"/>
+      <c r="M117" s="184"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E118" s="154" t="s">
         <v>48</v>
       </c>
@@ -7805,7 +10251,7 @@
       <c r="L118" s="154"/>
       <c r="M118" s="155"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E119" s="164" t="s">
         <v>118</v>
       </c>
@@ -7821,7 +10267,7 @@
       <c r="L119" s="154"/>
       <c r="M119" s="155"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E120" s="164" t="s">
         <v>122</v>
       </c>
@@ -7837,7 +10283,7 @@
       <c r="L120" s="154"/>
       <c r="M120" s="155"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E121" s="164"/>
       <c r="F121" s="157"/>
       <c r="G121" s="157"/>
@@ -7848,7 +10294,7 @@
       <c r="L121" s="154"/>
       <c r="M121" s="155"/>
     </row>
-    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E122" s="164"/>
       <c r="F122" s="157"/>
       <c r="G122" s="157"/>
@@ -7859,7 +10305,7 @@
       <c r="L122" s="154"/>
       <c r="M122" s="155"/>
     </row>
-    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F123" s="157"/>
       <c r="G123" s="157"/>
       <c r="H123" s="157"/>
@@ -7869,7 +10315,7 @@
       <c r="L123" s="154"/>
       <c r="M123" s="155"/>
     </row>
-    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E124" s="164"/>
       <c r="F124" s="157"/>
       <c r="G124" s="157"/>
@@ -7880,7 +10326,7 @@
       <c r="L124" s="154"/>
       <c r="M124" s="155"/>
     </row>
-    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E125" s="154"/>
       <c r="F125" s="157"/>
       <c r="G125" s="157"/>
@@ -7891,7 +10337,7 @@
       <c r="L125" s="154"/>
       <c r="M125" s="155"/>
     </row>
-    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E126" s="154"/>
       <c r="F126" s="157"/>
       <c r="G126" s="157"/>
@@ -7902,7 +10348,7 @@
       <c r="L126" s="154"/>
       <c r="M126" s="155"/>
     </row>
-    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E127" s="154"/>
       <c r="F127" s="157"/>
       <c r="G127" s="157"/>
@@ -7913,24 +10359,58 @@
       <c r="L127" s="165"/>
       <c r="M127" s="166"/>
     </row>
-    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="176" t="s">
+    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E128" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="177"/>
-      <c r="G128" s="177"/>
-      <c r="H128" s="177"/>
-      <c r="I128" s="177"/>
-      <c r="J128" s="178">
+      <c r="F128" s="193"/>
+      <c r="G128" s="193"/>
+      <c r="H128" s="193"/>
+      <c r="I128" s="193"/>
+      <c r="J128" s="194">
         <f>SUM(J118:J127)</f>
         <v>110347.66</v>
       </c>
-      <c r="K128" s="179"/>
+      <c r="K128" s="195"/>
       <c r="L128" s="167"/>
       <c r="M128" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="E108:K108"/>
     <mergeCell ref="E109:K109"/>
@@ -7947,40 +10427,6 @@
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="E52:I52"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
